--- a/Sajjad data/by_country_and_state/USA/CO.xlsx
+++ b/Sajjad data/by_country_and_state/USA/CO.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1066" uniqueCount="493">
   <si>
     <t>Business Name</t>
   </si>
@@ -110,6 +110,1386 @@
   </si>
   <si>
     <t>2026-10-24T01:23:10.833Z</t>
+  </si>
+  <si>
+    <t>Denver Dental Implants</t>
+  </si>
+  <si>
+    <t>+1 303-945-3483</t>
+  </si>
+  <si>
+    <t>Dental implants periodontist</t>
+  </si>
+  <si>
+    <t>1781 15th St, Denver, CO 80202, United States</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>FridayClosed; SaturdayClosed; SundayClosed; Monday7 AM–5 PM; Tuesday7 AM–5 PM; Wednesday7 AM–5 PM; Thursday7 AM–5 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Denver+Dental+Implants/data=!4m7!3m6!1s0x876c78c3f99bfe99:0xca7095112300f2cc!8m2!3d39.751509!4d-105.002595!16s%2Fg%2F11gzh8wt_!19sChIJmf6b-cN4bIcRzPIAIxGVcMo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T01:25:53.748Z</t>
+  </si>
+  <si>
+    <t>Choice Dental Office</t>
+  </si>
+  <si>
+    <t>(720) 731-0059</t>
+  </si>
+  <si>
+    <t>Emergency dental service</t>
+  </si>
+  <si>
+    <t>3604 W 50th Ave, Denver, CO 80221</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Choice+Dental+Office/data=!4m7!3m6!1s0x876b878c7c056621:0xee5d1ce45e521640!8m2!3d39.7873389!4d-105.0347919!16s%2Fg%2F11n4n9v_2b!19sChIJIWYFfIyHa4cRQBZSXuQcXe4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T18:56:06.304Z</t>
+  </si>
+  <si>
+    <t>Today Dental Care</t>
+  </si>
+  <si>
+    <t>(855) 526-7216</t>
+  </si>
+  <si>
+    <t>2532 Sheridan Blvd, Denver, CO 80214</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Today+Dental+Care/data=!4m7!3m6!1s0x876b8766193ff5c9:0x35171342e5073c8a!8m2!3d39.7536631!4d-105.052901!16s%2Fg%2F11y_k5507s!19sChIJyfU_GWaHa4cRijwH5UITFzU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T18:56:08.853Z</t>
+  </si>
+  <si>
+    <t>Central Park Modern Dentistry</t>
+  </si>
+  <si>
+    <t>(303) 785-8991</t>
+  </si>
+  <si>
+    <t>7505 E 35th Ave #304, Denver, CO 80238</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Central+Park+Modern+Dentistry/data=!4m7!3m6!1s0x876c7b9972c038d7:0xbde7be2ce0b05f9d!8m2!3d39.7659795!4d-104.9006983!16s%2Fg%2F11c1nqd9f6!19sChIJ1zjAcpl7bIcRnV-w4Cy-570?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T18:56:26.209Z</t>
+  </si>
+  <si>
+    <t>QuickCare Help Service</t>
+  </si>
+  <si>
+    <t>(855) 234-9795</t>
+  </si>
+  <si>
+    <t>Dental clinic</t>
+  </si>
+  <si>
+    <t>5191 Steele St, Denver, CO 80216</t>
+  </si>
+  <si>
+    <t>SaturdayOpen 24 hours</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/QuickCare+Help+Service/data=!4m7!3m6!1s0x876c7954aa740903:0x183d7037961d163b!8m2!3d39.7908616!4d-104.9502561!16s%2Fg%2F11zdjm54yj!19sChIJAwl0qlR5bIcROxYdljdwPRg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T18:56:28.969Z</t>
+  </si>
+  <si>
+    <t>Velora Teeth Whitening</t>
+  </si>
+  <si>
+    <t>(720) 296-2523</t>
+  </si>
+  <si>
+    <t>Teeth whitening service</t>
+  </si>
+  <si>
+    <t>4271 Lowell Blvd, Denver, CO 80211</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Velora+Teeth+Whitening/data=!4m7!3m6!1s0x876b87b28c88098b:0x31ed945968af497d!8m2!3d39.7756174!4d-105.0348061!16s%2Fg%2F11nqpkfxnc!19sChIJiwmIjLKHa4cRfUmvaFmU7TE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T18:57:05.748Z</t>
+  </si>
+  <si>
+    <t>Star Ranch Family Dental</t>
+  </si>
+  <si>
+    <t>(719) 442-1960</t>
+  </si>
+  <si>
+    <t>3695 Star Ranch Rd, Colorado Springs, CO 80906</t>
+  </si>
+  <si>
+    <t>Colorado Springs</t>
+  </si>
+  <si>
+    <t>4.1</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Star+Ranch+Family+Dental/data=!4m7!3m6!1s0x871343660546c26f:0x85e91c5495d59686!8m2!3d38.7753349!4d-104.8170245!16s%2Fg%2F1tlz_mzn!19sChIJb8JGBWZDE4cRhpbVlVQc6YU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T18:57:54.361Z</t>
+  </si>
+  <si>
+    <t>Professionals In DentistryLlc.</t>
+  </si>
+  <si>
+    <t>(719) 392-5300</t>
+  </si>
+  <si>
+    <t>Medical clinic</t>
+  </si>
+  <si>
+    <t>513 Kiva Rd, Colorado Springs, CO 80911</t>
+  </si>
+  <si>
+    <t>4.8</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Professionals+In+DentistryLlc./data=!4m7!3m6!1s0x871341bf1b988b5b:0x6357257158479ca4!8m2!3d38.7375239!4d-104.7249709!16s%2Fg%2F1tg2l3fq!19sChIJW4uYG79BE4cRpJxHWHElV2M?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T18:58:53.887Z</t>
+  </si>
+  <si>
+    <t>All Care Family Dental</t>
+  </si>
+  <si>
+    <t>(719) 579-8323</t>
+  </si>
+  <si>
+    <t>214 E Cheyenne Mountain Blvd, Colorado Springs, CO 80906</t>
+  </si>
+  <si>
+    <t>4.3</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/All+Care+Family+Dental/data=!4m7!3m6!1s0x871344a220e02b4d:0x6b0b892131bccf94!8m2!3d38.7902829!4d-104.823109!16s%2Fg%2F1tdylnvn!19sChIJTSvgIKJEE4cRlM-8MSGJC2s?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T18:58:55.745Z</t>
+  </si>
+  <si>
+    <t>Steven A Enea, DDS</t>
+  </si>
+  <si>
+    <t>(719) 388-8700</t>
+  </si>
+  <si>
+    <t>1975 Dominion Way Ste 100, Colorado Springs, CO 80918</t>
+  </si>
+  <si>
+    <t>4.6</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Steven+A+Enea,+DDS/data=!4m7!3m6!1s0x87134ef093c9bc49:0x203ac1f5a8d21ff6!8m2!3d38.922326!4d-104.7909597!16s%2Fg%2F1tffdng7!19sChIJSbzJk_BOE4cR9h_SqPXBOiA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:00:40.201Z</t>
+  </si>
+  <si>
+    <t>Springs Dental Service</t>
+  </si>
+  <si>
+    <t>(719) 851-6096</t>
+  </si>
+  <si>
+    <t>202 N Union Blvd, Colorado Springs, CO 80909</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Springs+Dental+Service/data=!4m7!3m6!1s0x8713459d374a56a7:0xebb2931de3265bbb!8m2!3d38.8363753!4d-104.795037!16s%2Fg%2F11vt8b66sg!19sChIJp1ZKN51FE4cRu1sm4x2Tsus?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:01:02.501Z</t>
+  </si>
+  <si>
+    <t>21st Street Dental Group</t>
+  </si>
+  <si>
+    <t>(719) 368-8813</t>
+  </si>
+  <si>
+    <t>2620 Tenderfoot Hill St #210, Colorado Springs, CO 80906</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/21st+Street+Dental+Group/data=!4m7!3m6!1s0x87135ac79c5f21a5:0xd1d3f4bb0eda1a9d!8m2!3d38.7956115!4d-104.8131294!16s%2Fg%2F11cs6k7z7b!19sChIJpSFfnMdaE4cRnRraDrv009E?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:01:04.855Z</t>
+  </si>
+  <si>
+    <t>Karl P. Lackler, DDS, MS</t>
+  </si>
+  <si>
+    <t>(719) 574-4867</t>
+  </si>
+  <si>
+    <t>685 Citadel Dr E #200a, Colorado Springs, CO 80909</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>SaturdayClosed; SundayClosed; MondayClosed; Tuesday8 AM–5 PM; Wednesday8 AM–5 PM; Thursday8 AM–5 PM; Friday8 AM–5 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Karl+P.+Lackler,+DDS,+MS/data=!4m7!3m6!1s0x871345cff188ac7f:0xf37183e1d418c9d6!8m2!3d38.8424644!4d-104.7582855!16s%2Fg%2F1tyzzfrn!19sChIJf6yI8c9FE4cR1skY1OGDcfM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:02:55.733Z</t>
+  </si>
+  <si>
+    <t>James R. Norris, DDS, MS</t>
+  </si>
+  <si>
+    <t>(719) 599-7760</t>
+  </si>
+  <si>
+    <t>1975 Research Pkwy Ste 305, Colorado Springs, CO 80920</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/James+R.+Norris,+DDS,+MS/data=!4m7!3m6!1s0x87134c2c69d76985:0xb4af0cca331fd1c0!8m2!3d38.9578028!4d-104.7949!16s%2Fg%2F11c70cknz5!19sChIJhWnXaSxME4cRwNEfM8oMr7Q?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:02:58.235Z</t>
+  </si>
+  <si>
+    <t>Lowell District Dental - Dr. Arnold Cullum</t>
+  </si>
+  <si>
+    <t>(719) 591-2004</t>
+  </si>
+  <si>
+    <t>251 E Fountain Blvd #100, Colorado Springs, CO 80903</t>
+  </si>
+  <si>
+    <t>3.3</t>
+  </si>
+  <si>
+    <t>Saturday10 AM–2 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Lowell+District+Dental+-+Dr.+Arnold+Cullum/data=!4m7!3m6!1s0x871345cff188ac7f:0x33763eee4f4876f1!8m2!3d38.8214474!4d-104.82104!16s%2Fg%2F1tfyf0fm!19sChIJf6yI8c9FE4cR8XZIT-4-djM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:03:00.798Z</t>
+  </si>
+  <si>
+    <t>Clinica Dental Latina</t>
+  </si>
+  <si>
+    <t>(303) 364-9831</t>
+  </si>
+  <si>
+    <t>11175 E Mississippi Ave Ste 100, Aurora, CO 80012</t>
+  </si>
+  <si>
+    <t>Aurora</t>
+  </si>
+  <si>
+    <t>Saturday9 AM–3:30 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Clinica+Dental+Latina/data=!4m7!3m6!1s0x876c7d39cd2c0fab:0x2a07e04b37e96d19!8m2!3d39.6971368!4d-104.8580599!16s%2Fg%2F1tctm8lf!19sChIJqw8szTl9bIcRGW3pN0vgByo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:03:16.248Z</t>
+  </si>
+  <si>
+    <t>Aurora Family Dental Care</t>
+  </si>
+  <si>
+    <t>(303) 344-1227</t>
+  </si>
+  <si>
+    <t>14221 E 4th Ave #222, Aurora, CO 80011</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Aurora+Family+Dental+Care/data=!4m7!3m6!1s0x876c6321e817e5c1:0xc971ee2426ae4126!8m2!3d39.723156!4d-104.822933!16s%2Fg%2F1w0r0dcv!19sChIJweUX6CFjbIcRJkGuJiTucck?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:03:20.477Z</t>
+  </si>
+  <si>
+    <t>Aurora Dental Group</t>
+  </si>
+  <si>
+    <t>(303) 745-2052</t>
+  </si>
+  <si>
+    <t>380 S Potomac St Unit 135, Aurora, CO 80012</t>
+  </si>
+  <si>
+    <t>3.5</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Aurora+Dental+Group/data=!4m7!3m6!1s0x876c628fe9546351:0xf6a6fe5949a9bf01!8m2!3d39.7085262!4d-104.8278826!16s%2Fg%2F1ydpvbhy7!19sChIJUWNU6Y9ibIcRAb-pSVn-pvY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:03:26.844Z</t>
+  </si>
+  <si>
+    <t>Gateway Park Family &amp; Cosmetic Dentistry</t>
+  </si>
+  <si>
+    <t>(303) 307-8282</t>
+  </si>
+  <si>
+    <t>3471 N Salida St #60, Aurora, CO 80011</t>
+  </si>
+  <si>
+    <t>4.5</t>
+  </si>
+  <si>
+    <t>942</t>
+  </si>
+  <si>
+    <t>Saturday8 AM–12 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Gateway+Park+Family+%26+Cosmetic+Dentistry/data=!4m7!3m6!1s0x876c638ac38b0f5f:0x40e3b95257274292!8m2!3d39.7642636!4d-104.7764162!16s%2Fg%2F1tycx434!19sChIJXw-Lw4pjbIcRkkInV1K540A?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:04:57.540Z</t>
+  </si>
+  <si>
+    <t>Smoky Hill Family Dentistry</t>
+  </si>
+  <si>
+    <t>(303) 699-8788</t>
+  </si>
+  <si>
+    <t>16629 E Smoky Hill Rd, Aurora, CO 80015</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Smoky+Hill+Family+Dentistry/data=!4m7!3m6!1s0x876c891dcf238889:0x44262aa235ce7df3!8m2!3d39.628472!4d-104.794898!16s%2Fg%2F1td13s2r!19sChIJiYgjzx2JbIcR833ONaIqJkQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:05:36.646Z</t>
+  </si>
+  <si>
+    <t>Kids Smiles Colorado</t>
+  </si>
+  <si>
+    <t>(303) 339-1155</t>
+  </si>
+  <si>
+    <t>Pediatric dentist</t>
+  </si>
+  <si>
+    <t>14001 E Iliff Ave Ste, Ste 120, Aurora, CO 80014</t>
+  </si>
+  <si>
+    <t>Saturday8 AM–1 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Kids+Smiles+Colorado/data=!4m7!3m6!1s0x876c89a380d7044d:0x201050fa7b9a0c7c!8m2!3d39.6760689!4d-104.8264224!16s%2Fg%2F11l_0cz43h!19sChIJTQTXgKOJbIcRfAyae_pQECA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:06:37.633Z</t>
+  </si>
+  <si>
+    <t>Ken Allen, DDS</t>
+  </si>
+  <si>
+    <t>(970) 221-3700</t>
+  </si>
+  <si>
+    <t>2117 Custer Dr, Fort Collins, CO 80525</t>
+  </si>
+  <si>
+    <t>Fort Collins</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Ken+Allen,+DDS/data=!4m7!3m6!1s0x87694bb46ccc4519:0x62dab13a200aa49a!8m2!3d40.549524!4d-105.0371251!16s%2Fg%2F11nc5w925d!19sChIJGUXMbLRLaYcRmqQKIDqx2mI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:09:53.378Z</t>
+  </si>
+  <si>
+    <t>Dr. Stephen Pauly</t>
+  </si>
+  <si>
+    <t>(970) 484-4255</t>
+  </si>
+  <si>
+    <t>1513 Riverside Ave, Fort Collins, CO 80524</t>
+  </si>
+  <si>
+    <t>2.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Stephen+Pauly/data=!4m7!3m6!1s0x87694ad8ed2eaaab:0x19697c2d600f358f!8m2!3d40.5723701!4d-105.0478854!16s%2Fg%2F11qgb7vm54!19sChIJq6ou7dhKaYcRjzUPYC18aRk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:11:40.766Z</t>
+  </si>
+  <si>
+    <t>Board Certified Pediatric Dentistry</t>
+  </si>
+  <si>
+    <t>(970) 493-2254</t>
+  </si>
+  <si>
+    <t>2105 Bighorn Dr STE 202, Fort Collins, CO 80525</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Board+Certified+Pediatric+Dentistry/data=!4m7!3m6!1s0x87694b5687ea55a9:0xd5e7c16ce4346b2b!8m2!3d40.535082!4d-105.0388589!16s%2Fg%2F11g9vt7307!19sChIJqVXqh1ZLaYcRK2s05GzB59U?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:11:43.354Z</t>
+  </si>
+  <si>
+    <t>Dr. Shahnaz Formoli Emergency Dental Service</t>
+  </si>
+  <si>
+    <t>(970) 572-7800</t>
+  </si>
+  <si>
+    <t>215 S Howes St, Fort Collins, CO 80521</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Shahnaz+Formoli+Emergency+Dental+Service/data=!4m7!3m6!1s0x87694b77aa778f4d:0x3519bcbb29de6514!8m2!3d40.5851405!4d-105.0804809!16s%2Fg%2F11nvf7b607!19sChIJTY93qndLaYcRFGXeKbu8GTU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:12:12.345Z</t>
+  </si>
+  <si>
+    <t>Fort Collins Dentistry Now</t>
+  </si>
+  <si>
+    <t>(970) 816-8743</t>
+  </si>
+  <si>
+    <t>1825 E Harmony Rd Ste 7b, Fort Collins, CO 80528</t>
+  </si>
+  <si>
+    <t>3.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Fort+Collins+Dentistry+Now/data=!4m7!3m6!1s0x87694d7464a41445:0xefebbb6a272e626a!8m2!3d40.5229211!4d-105.0431512!16s%2Fg%2F11vbff052y!19sChIJRRSkZHRNaYcRamIuJ2q76-8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:12:14.628Z</t>
+  </si>
+  <si>
+    <t>Urgent Dentist Connect</t>
+  </si>
+  <si>
+    <t>(970) 994-0030</t>
+  </si>
+  <si>
+    <t>5000 Goodman St Unit 101, Timnath, CO 80547</t>
+  </si>
+  <si>
+    <t>Timnath</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Urgent+Dentist+Connect/data=!4m7!3m6!1s0x876eb322c76bce09:0xdfd5a42fe5c7ec5!8m2!3d40.5173778!4d-104.9605756!16s%2Fg%2F11zzryn5l_!19sChIJCc5rxyKzbocRxX5c_kJa_Q0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:12:17.021Z</t>
+  </si>
+  <si>
+    <t>FC Prime Dental Care</t>
+  </si>
+  <si>
+    <t>(970) 709-0239</t>
+  </si>
+  <si>
+    <t>117 W Monroe Dr, Fort Collins, CO 80525</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/FC+Prime+Dental+Care/data=!4m7!3m6!1s0x87694bd17ab1345f:0xa9f6003f5b653bd0!8m2!3d40.539731!4d-105.0784093!16s%2Fg%2F11vr24g_08!19sChIJXzSxetFLaYcR0DtlWz8A9qk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:12:42.184Z</t>
+  </si>
+  <si>
+    <t>Dr. James C. Braun, DDS</t>
+  </si>
+  <si>
+    <t>(970) 221-2444</t>
+  </si>
+  <si>
+    <t>1136 E Stuart St Ste 4103, Fort Collins, CO 80525</t>
+  </si>
+  <si>
+    <t>160</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+James+C.+Braun,+DDS/data=!4m7!3m6!1s0x87694b18c6a3ee99:0xa05f2faac3f21eb1!8m2!3d40.5641161!4d-105.0575223!16s%2Fg%2F1tfjg0bj!19sChIJme6jxhhLaYcRsR7yw6ovX6A?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:13:26.811Z</t>
+  </si>
+  <si>
+    <t>Fox Point</t>
+  </si>
+  <si>
+    <t>(303) 989-3192</t>
+  </si>
+  <si>
+    <t>Business center</t>
+  </si>
+  <si>
+    <t>W Jewell Ave, Lakewood, CO 80228</t>
+  </si>
+  <si>
+    <t>Lakewood</t>
+  </si>
+  <si>
+    <t>4.4</t>
+  </si>
+  <si>
+    <t>544</t>
+  </si>
+  <si>
+    <t>Saturday9:30 AM–8:30 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Fox+Point/data=!4m7!3m6!1s0x876b83b130360693:0xffe77d1949f87481!8m2!3d39.6826351!4d-105.1558871!16s%2Fg%2F11h1dggjmk!19sChIJkwY2MLGDa4cRgXT4SRl95_8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:15:02.527Z</t>
+  </si>
+  <si>
+    <t>Green Gables Dental</t>
+  </si>
+  <si>
+    <t>(720) 442-8256</t>
+  </si>
+  <si>
+    <t>7586 W Jewell Ave unit 2-303, Lakewood, CO 80232</t>
+  </si>
+  <si>
+    <t>3.7</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Green+Gables+Dental/data=!4m7!3m6!1s0x876b81ab408fffff:0x86afd1d9a385977c!8m2!3d39.6817218!4d-105.0803559!16s%2Fg%2F11hd6_268_!19sChIJ__-PQKuBa4cRfJeFo9nRr4Y?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:15:20.186Z</t>
+  </si>
+  <si>
+    <t>Westgate Family Dentistry</t>
+  </si>
+  <si>
+    <t>(303) 980-4800</t>
+  </si>
+  <si>
+    <t>2323 S Wadsworth Blvd Unit 102, Lakewood, CO 80227</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Westgate+Family+Dentistry/data=!4m7!3m6!1s0x876b81ef421d329f:0x8ca42fb8f395e4a!8m2!3d39.6746927!4d-105.0819544!16s%2Fg%2F11jvqgjcz6!19sChIJnzIdQu-Ba4cRSl45j_tCygg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:15:46.174Z</t>
+  </si>
+  <si>
+    <t>Dental Reach</t>
+  </si>
+  <si>
+    <t>(720) 856-6178</t>
+  </si>
+  <si>
+    <t>10600 W Alameda Ave Ste 126, Lakewood, CO 80226</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Reach/data=!4m7!3m6!1s0x876b81f013740d7b:0x7556a7387882b96f!8m2!3d39.7104063!4d-105.1171275!16s%2Fg%2F11zxj5rxgq!19sChIJew10E_CBa4cRb7mCeDinVnU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:16:41.554Z</t>
+  </si>
+  <si>
+    <t>North Wash Med &amp; Dental Clinic</t>
+  </si>
+  <si>
+    <t>(303) 451-8081</t>
+  </si>
+  <si>
+    <t>9981 Washington St #24, Thornton, CO 80229</t>
+  </si>
+  <si>
+    <t>Thornton</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/North+Wash+Med+%26+Dental+Clinic/data=!4m7!3m6!1s0x876c76f39fa533b1:0xc7adcc1994e43a77!8m2!3d39.8776953!4d-104.9783013!16s%2Fg%2F1tf48n36!19sChIJsTOln_N2bIcRdzrklBnMrcc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:17:59.226Z</t>
+  </si>
+  <si>
+    <t>Emergency Dentist Source</t>
+  </si>
+  <si>
+    <t>(720) 791-0080</t>
+  </si>
+  <si>
+    <t>1360 Horizon Ave Unit 111, Lafayette, CO 80026</t>
+  </si>
+  <si>
+    <t>Lafayette</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Emergency+Dentist+Source/data=!4m7!3m6!1s0x876bf5ff6961d529:0x36354fbc2a1902b7!8m2!3d39.979604!4d-105.066914!16s%2Fg%2F11p1rg9m4r!19sChIJKdVhaf_1a4cRtwIZKrxPNTY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:19:55.192Z</t>
+  </si>
+  <si>
+    <t>Jenna Hyer, DDS, MS</t>
+  </si>
+  <si>
+    <t>(303) 457-9617</t>
+  </si>
+  <si>
+    <t>11178 Huron St, Northglenn, CO 80234</t>
+  </si>
+  <si>
+    <t>Northglenn</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Jenna+Hyer,+DDS,+MS/data=!4m7!3m6!1s0x876c872782282107:0xcddc8e15cd716759!8m2!3d39.8992866!4d-104.9957052!16s%2Fg%2F11kx9byk0z!19sChIJByEogieHbIcRWWdxzRWO3M0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:21:53.216Z</t>
+  </si>
+  <si>
+    <t>Dr. Mark A. Wheeler, DMD</t>
+  </si>
+  <si>
+    <t>(303) 469-6375</t>
+  </si>
+  <si>
+    <t>899 US-287 #100, Broomfield, CO 80020</t>
+  </si>
+  <si>
+    <t>Broomfield</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Mark+A.+Wheeler,+DMD/data=!4m7!3m6!1s0x876b8b087fc2ddcb:0x9fb09140607c2212!8m2!3d39.9276467!4d-105.0916234!16s%2Fg%2F1tdcgvyq!19sChIJy93CfwiLa4cREiJ8YECRsJ8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:21:56.415Z</t>
+  </si>
+  <si>
+    <t>Dr.Chien Dental Office</t>
+  </si>
+  <si>
+    <t>(303) 288-0888</t>
+  </si>
+  <si>
+    <t>500 84th Ave Unit E3, Thornton, CO 80229</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.Chien+Dental+Office/data=!4m7!3m6!1s0x876c7708bc74b803:0x8b7a48d195bf727f!8m2!3d39.8474531!4d-104.9811491!16s%2Fg%2F1tfw3jgp!19sChIJA7h0vAh3bIcRf3K_ldFIeos?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:21:58.886Z</t>
+  </si>
+  <si>
+    <t>Dr. Robert Mcbride</t>
+  </si>
+  <si>
+    <t>(303) 920-9145</t>
+  </si>
+  <si>
+    <t>12880 Colorado Blvd #120, Thornton, CO 80241</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Robert+Mcbride/data=!4m7!3m6!1s0x876c73800604b929:0x25d43f193148156c!8m2!3d39.9300767!4d-104.9400103!16s%2Fg%2F11p07b0ml5!19sChIJKbkEBoBzbIcRbBVIMRk_1CU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:22:01.206Z</t>
+  </si>
+  <si>
+    <t>Advanced Dental Arts</t>
+  </si>
+  <si>
+    <t>(303) 422-2020</t>
+  </si>
+  <si>
+    <t>8770 Wadsworth Blvd H, Arvada, CO 80003</t>
+  </si>
+  <si>
+    <t>Arvada</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Advanced+Dental+Arts/data=!4m7!3m6!1s0x876b8907eb654aa5:0x74472bce629634f1!8m2!3d39.8555941!4d-105.0799869!16s%2Fg%2F1tf43fw2!19sChIJpUpl6weJa4cR8TSWYs4rR3Q?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:23:23.379Z</t>
+  </si>
+  <si>
+    <t>Holmes Caron B DDS</t>
+  </si>
+  <si>
+    <t>(303) 420-7100</t>
+  </si>
+  <si>
+    <t>6355 Ward Rd #410, Arvada, CO 80004</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Holmes+Caron+B+DDS/data=!4m7!3m6!1s0x876b8f459c6cb5bd:0xe093407941952124!8m2!3d39.8116791!4d-105.1383651!16s%2Fg%2F1w112p43!19sChIJvbVsnEWPa4cRJCGVQXlAk-A?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:24:47.843Z</t>
+  </si>
+  <si>
+    <t>Dr. Jeffrey C. Moser, DDS</t>
+  </si>
+  <si>
+    <t>(303) 657-9006</t>
+  </si>
+  <si>
+    <t>7578 Sheridan Blvd, Arvada, CO 80003</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Jeffrey+C.+Moser,+DDS/data=!4m7!3m6!1s0x876b883ee6926eb3:0x8c9b6827a5f5173!8m2!3d39.8338339!4d-105.0522732!16s%2Fg%2F1tjyv2mm!19sChIJs26S5j6Ia4cRc1FfeoK2yQg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:24:54.116Z</t>
+  </si>
+  <si>
+    <t>Family Hair Care</t>
+  </si>
+  <si>
+    <t>(303) 960-4228</t>
+  </si>
+  <si>
+    <t>Barber shop</t>
+  </si>
+  <si>
+    <t>7564 Grant Pl, Arvada, CO 80002</t>
+  </si>
+  <si>
+    <t>4.9</t>
+  </si>
+  <si>
+    <t>Saturday9 AM–5 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Family+Hair+Care/data=!4m7!3m6!1s0x876b87cd6867498d:0xf87b8e93076c29e7!8m2!3d39.8009944!4d-105.0809978!16s%2Fg%2F1tdqc1j4!19sChIJjUlnaM2Ha4cR5ylsB5OOe_g?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:25:00.970Z</t>
+  </si>
+  <si>
+    <t>Mile High Smile Orthodontics – Dr. James Gallagher</t>
+  </si>
+  <si>
+    <t>(303) 424-4048</t>
+  </si>
+  <si>
+    <t>Orthodontist</t>
+  </si>
+  <si>
+    <t>7913 Allison Way #201, Arvada, CO 80005</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Mile+High+Smile+Orthodontics+%E2%80%93+Dr.+James+Gallagher/data=!4m7!3m6!1s0x876b88fbbb6612eb:0x6e85192a58f97c4d!8m2!3d39.839257!4d-105.08708!16s%2Fg%2F1tdlvrvk!19sChIJ6xJmu_uIa4cRTXz5WCoZhW4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:25:25.608Z</t>
+  </si>
+  <si>
+    <t>Rapid Dental Connect</t>
+  </si>
+  <si>
+    <t>(303) 647-3624</t>
+  </si>
+  <si>
+    <t>5127 W 64th Ave, Arvada, CO 80003</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Rapid+Dental+Connect/data=!4m7!3m6!1s0x876b8923b7e05761:0xcd797d269f1adb01!8m2!3d39.813325!4d-105.0511224!16s%2Fg%2F11p1b1fqgx!19sChIJYVfgtyOJa4cRAdsanyZ9ec0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:25:48.957Z</t>
+  </si>
+  <si>
+    <t>Da Vinci Teeth Whitening</t>
+  </si>
+  <si>
+    <t>(720) 421-1906</t>
+  </si>
+  <si>
+    <t>5027 W 64th Ave, Arvada, CO 80003</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Da+Vinci+Teeth+Whitening/data=!4m7!3m6!1s0x876b88873a3474cb:0xf862d64d1a227def!8m2!3d39.8134494!4d-105.0510203!16s%2Fg%2F11b5wdh4y_!19sChIJy3Q0OoeIa4cR730iGk3WYvg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:26:32.226Z</t>
+  </si>
+  <si>
+    <t>ProSmile</t>
+  </si>
+  <si>
+    <t>(303) 431-5830</t>
+  </si>
+  <si>
+    <t>10135 W 38th Ave, Wheat Ridge, CO 80033</t>
+  </si>
+  <si>
+    <t>Wheat Ridge</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/ProSmile/data=!4m7!3m6!1s0x876b866455eac4b3:0xd7f8e150413651b!8m2!3d39.7700111!4d-105.1111847!16s%2Fg%2F1tppsg1x!19sChIJs8TqVWSGa4cRG2UTBBWOfw0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:26:45.352Z</t>
+  </si>
+  <si>
+    <t>Gregg T. Rogers, DDS - Practice Limited to Periodontics</t>
+  </si>
+  <si>
+    <t>(303) 424-5463</t>
+  </si>
+  <si>
+    <t>Periodontist</t>
+  </si>
+  <si>
+    <t>8749 Wadsworth Blvd, Arvada, CO 80003</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Gregg+T.+Rogers,+DDS+-+Practice+Limited+to+Periodontics/data=!4m7!3m6!1s0x876b8907ca625289:0xd3e10802da2e898a!8m2!3d39.855006!4d-105.0828221!16s%2Fg%2F1tk9r7ry!19sChIJiVJiygeJa4cRioku2gII4dM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:27:02.090Z</t>
+  </si>
+  <si>
+    <t>Arvada Periodonitcs</t>
+  </si>
+  <si>
+    <t>(303) 424-7757</t>
+  </si>
+  <si>
+    <t>7502 W 80th Ave Unit 100, Arvada, CO 80003</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Arvada+Periodonitcs/data=!4m7!3m6!1s0x876b88f8b1b7494b:0xdfe0179aaaff66f4!8m2!3d39.841341!4d-105.0799527!16s%2Fg%2F1262jsz1d!19sChIJS0m3sfiIa4cR9Gb_qpoX4N8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:27:08.630Z</t>
+  </si>
+  <si>
+    <t>Amazing Smiles</t>
+  </si>
+  <si>
+    <t>(303) 424-5439</t>
+  </si>
+  <si>
+    <t>7236 N Federal Blvd #100, Westminster, CO 80030</t>
+  </si>
+  <si>
+    <t>Westminster</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Amazing+Smiles/data=!4m7!3m6!1s0x876c77e42f39f9eb:0x978db76069100d48!8m2!3d39.828112!4d-105.0241378!16s%2Fg%2F1tcvzxpp!19sChIJ6_k5L-R3bIcRSA0QaWC3jZc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:27:24.311Z</t>
+  </si>
+  <si>
+    <t>14 Peaks Dentistry</t>
+  </si>
+  <si>
+    <t>(303) 429-1426</t>
+  </si>
+  <si>
+    <t>7629 W 88th Ave, Westminster, CO 80005</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/14+Peaks+Dentistry/data=!4m7!3m6!1s0x876b883772283591:0x2fecc1de5e323d87!8m2!3d39.8591964!4d-105.0830937!16s%2Fg%2F1tcty0wg!19sChIJkTUocjeIa4cRhz0yXt7B7C8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:29:16.837Z</t>
+  </si>
+  <si>
+    <t>Parish Dural L DDS</t>
+  </si>
+  <si>
+    <t>(303) 425-6565</t>
+  </si>
+  <si>
+    <t>10835 N Dover St, Broomfield, CO 80021</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Parish+Dural+L+DDS/data=!4m7!3m6!1s0x876b8bdb0f8a3553:0xc8a8fe6b8e51b01d!8m2!3d39.8930865!4d-105.0947427!16s%2Fg%2F1th5d18r!19sChIJUzWKD9uLa4cRHbBRjmv-qMg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:29:31.828Z</t>
+  </si>
+  <si>
+    <t>Urgent Dental Hub</t>
+  </si>
+  <si>
+    <t>(303) 586-0763</t>
+  </si>
+  <si>
+    <t>8778 Wolff Ct #102, Westminster, CO 80031</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Urgent+Dental+Hub/data=!4m7!3m6!1s0x876b898166c97c43:0x42e8ff3a397ddc2f!8m2!3d39.8559207!4d-105.0487308!16s%2Fg%2F11zxx8rd9_!19sChIJQ3zJZoGJa4cRL9x9OTr_6EI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:29:51.041Z</t>
+  </si>
+  <si>
+    <t>Emergency Dental Station</t>
+  </si>
+  <si>
+    <t>(720) 764-0971</t>
+  </si>
+  <si>
+    <t>643 S Arthur Ave, Louisville, CO 80027</t>
+  </si>
+  <si>
+    <t>Louisville</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Emergency+Dental+Station/data=!4m7!3m6!1s0x876b8b1ec2c47b9b:0x261febb04165057d!8m2!3d39.96043!4d-105.12359!16s%2Fg%2F11zy8_r3wy!19sChIJm3vEwh6La4cRfQVlQbDrHyY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:29:53.607Z</t>
+  </si>
+  <si>
+    <t>Dr. Tommy Yun</t>
+  </si>
+  <si>
+    <t>(303) 410-4950</t>
+  </si>
+  <si>
+    <t>10442 Town Center Dr #100, Westminster, CO 80021</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Tommy+Yun/data=!4m7!3m6!1s0x876b89809c5d72a5:0x18e41a38b2ede1ef!8m2!3d39.8874026!4d-105.0752496!16s%2Fg%2F11rwxg1btc!19sChIJpXJdnICJa4cR7-Htsjga5Bg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:31:03.577Z</t>
+  </si>
+  <si>
+    <t>Down To Earth Dental</t>
+  </si>
+  <si>
+    <t>(719) 546-0404</t>
+  </si>
+  <si>
+    <t>1407 W 29th St, Pueblo, CO 81008</t>
+  </si>
+  <si>
+    <t>Pueblo</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Down+To+Earth+Dental/data=!4m7!3m6!1s0x8713a239ad07f393:0xc1275dd80ea6bb41!8m2!3d38.2981247!4d-104.6261045!16s%2Fg%2F1tg6k_qk!19sChIJk_MHrTmiE4cRQbumDthdJ8E?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:31:18.905Z</t>
+  </si>
+  <si>
+    <t>Dr. Sarah Mitchell Dental</t>
+  </si>
+  <si>
+    <t>(719) 415-4085</t>
+  </si>
+  <si>
+    <t>600 N Main St, Pueblo, CO 81003</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Sarah+Mitchell+Dental/data=!4m7!3m6!1s0x8713a3ee09bf2735:0x6bffc1b4d737a996!8m2!3d38.2726931!4d-104.6083682!16s%2Fg%2F11zfhp3nvq!19sChIJNSe_Ce6jE4cRlqk317TB_2s?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:31:22.081Z</t>
+  </si>
+  <si>
+    <t>Belmont Dental Center</t>
+  </si>
+  <si>
+    <t>(719) 544-5340</t>
+  </si>
+  <si>
+    <t>1560 Bonforte Blvd, Pueblo, CO 81001</t>
+  </si>
+  <si>
+    <t>4.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Belmont+Dental+Center/data=!4m7!3m6!1s0x8713a35b336cab95:0xc03553dd1fe09b61!8m2!3d38.2923571!4d-104.5918266!16s%2Fg%2F11t_zd1b9n!19sChIJlatsM1ujE4cRYZvgH91TNcA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:31:24.485Z</t>
+  </si>
+  <si>
+    <t>Southern Colorado Dental Anesthesiology</t>
+  </si>
+  <si>
+    <t>(719) 286-0733</t>
+  </si>
+  <si>
+    <t>1225 N Main St Ste 206, Pueblo, CO 81003</t>
+  </si>
+  <si>
+    <t>Saturday6 AM–5 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Southern+Colorado+Dental+Anesthesiology/data=!4m7!3m6!1s0x8713a331292e5045:0x21fbe9b9e4014933!8m2!3d38.2787575!4d-104.6089763!16s%2Fg%2F11n0vv0jm2!19sChIJRVAuKTGjE4cRM0kB5Lnp-yE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:31:28.930Z</t>
+  </si>
+  <si>
+    <t>Dental Hygiene Services</t>
+  </si>
+  <si>
+    <t>(719) 542-2489</t>
+  </si>
+  <si>
+    <t>2099 E US Hwy 50 #180, Pueblo, CO 81008</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Hygiene+Services/data=!4m7!3m6!1s0x8713a21eed467a41:0xf493f39c87e44e7c!8m2!3d38.2458265!4d-104.5734946!16s%2Fg%2F1trrdnjs!19sChIJQXpG7R6iE4cRfE7kh5zzk_Q?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:31:31.260Z</t>
+  </si>
+  <si>
+    <t>Dr. Jeremy Thomas</t>
+  </si>
+  <si>
+    <t>(719) 545-2468</t>
+  </si>
+  <si>
+    <t>1100 Eagleridge Blvd, Pueblo, CO 81008</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Jeremy+Thomas/data=!4m7!3m6!1s0x8713a18624daaaab:0xe3195bc9bc87ae8c!8m2!3d38.3198489!4d-104.623096!16s%2Fg%2F11rwxfdmnq!19sChIJq6raJIahE4cRjK6HvMlbGeM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:31:33.756Z</t>
+  </si>
+  <si>
+    <t>Great Smiles Complete Dentistry</t>
+  </si>
+  <si>
+    <t>(866) 332-0768</t>
+  </si>
+  <si>
+    <t>2037 Jerry Murphy Rd #202, Pueblo, CO 81001</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Great+Smiles+Complete+Dentistry/data=!4m7!3m6!1s0x8713a3c5bf4e69c1:0x676e2ba3d733b2de!8m2!3d38.3054166!4d-104.598661!16s%2Fg%2F1262xh_ym!19sChIJwWlOv8WjE4cR3rIz16Mrbmc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:31:36.742Z</t>
+  </si>
+  <si>
+    <t>Dr. Anthony I. Oreskovich, DDS.</t>
+  </si>
+  <si>
+    <t>(719) 542-8182</t>
+  </si>
+  <si>
+    <t>1111 Pueblo Blvd Way #140, Pueblo, CO 81005</t>
+  </si>
+  <si>
+    <t>4.2</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Anthony+I.+Oreskovich,+DDS./data=!4m7!3m6!1s0x8713980b9a3d571f:0x970fd718cf2a5a62!8m2!3d38.245596!4d-104.662255!16s%2Fg%2F1vgx166d!19sChIJH1c9mguYE4cRYloqzxjXD5c?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:31:39.704Z</t>
+  </si>
+  <si>
+    <t>Autobee Dental Center</t>
+  </si>
+  <si>
+    <t>(719) 543-8940</t>
+  </si>
+  <si>
+    <t>108 E Pitkin Ave, Pueblo, CO 81004</t>
+  </si>
+  <si>
+    <t>2.3</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Autobee+Dental+Center/data=!4m7!3m6!1s0x8713a2e87b9f57a3:0x3934fc79e1f9c2e1!8m2!3d38.2565764!4d-104.6244353!16s%2Fg%2F11cjgbhyxz!19sChIJo1efe-iiE4cR4cL54Xn8NDk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:31:42.027Z</t>
+  </si>
+  <si>
+    <t>Complete Family Dental Care</t>
+  </si>
+  <si>
+    <t>(719) 583-0555</t>
+  </si>
+  <si>
+    <t>401 W 12th St, Pueblo, CO 81003</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Complete+Family+Dental+Care/data=!4m7!3m6!1s0x8713a3aacc933ba3:0xb59bff94532ab465!8m2!3d38.278213!4d-104.611981!16s%2Fg%2F1tcv6s7q!19sChIJozuTzKqjE4cRZbQqU5T_m7U?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:31:44.544Z</t>
+  </si>
+  <si>
+    <t>family dental</t>
+  </si>
+  <si>
+    <t>(877) 280-0933</t>
+  </si>
+  <si>
+    <t>Health counselor</t>
+  </si>
+  <si>
+    <t>1637 Cherrywood Ln, Pueblo, CO 81005</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>Saturday8 AM–6 PM; SundayClosed; Monday8 AM–6 PM; Tuesday8 AM–6 PM; Wednesday8 AM–6 PM; Thursday8 AM–6 PM; Friday8 AM–6 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/family+dental/data=!4m7!3m6!1s0x8713a3f8b4c498d3:0xa48f5f2021d6b501!8m2!3d38.2402632!4d-104.6498321!16s%2Fg%2F11vlj_htl3!19sChIJ05jEtPijE4cRAbXWISBfj6Q?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:33:44.244Z</t>
+  </si>
+  <si>
+    <t>Kristi Craig</t>
+  </si>
+  <si>
+    <t>(719) 545-3838</t>
+  </si>
+  <si>
+    <t>2208 Thatcher Ave, Pueblo, CO 81004</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Kristi+Craig/data=!4m7!3m6!1s0x8713a29365a55555:0xba3fd77728f3529e!8m2!3d38.2583763!4d-104.6374385!16s%2Fg%2F11pkfqxtb_!19sChIJVVWlZZOiE4cRnlLzKHfXP7o?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:33:46.543Z</t>
+  </si>
+  <si>
+    <t>Dr. Brian Scott</t>
+  </si>
+  <si>
+    <t>(719) 545-2722</t>
+  </si>
+  <si>
+    <t>1641 Horseshoe Dr, Pueblo, CO 81001</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Brian+Scott/data=!4m7!3m6!1s0x8713a3bda2715555:0x8a45794a6af0dc7e!8m2!3d38.2926097!4d-104.5903284!16s%2Fg%2F11rwxg8fhm!19sChIJVVVxor2jE4cRftzwakp5RYo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:34:35.417Z</t>
+  </si>
+  <si>
+    <t>Altra Dental Lab.</t>
+  </si>
+  <si>
+    <t>(719) 545-1810</t>
+  </si>
+  <si>
+    <t>Dental laboratory</t>
+  </si>
+  <si>
+    <t>1314 E Evans Ave, Pueblo, CO 81004</t>
+  </si>
+  <si>
+    <t>3.8</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Altra+Dental+Lab./data=!4m7!3m6!1s0x8713a2c557e449d3:0xa72076937b267ede!8m2!3d38.2434761!4d-104.6146453!16s%2Fg%2F1260ssz64!19sChIJ00nkV8WiE4cR3n4me5N2IKc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:35:03.920Z</t>
+  </si>
+  <si>
+    <t>Smith Brady T DDS</t>
+  </si>
+  <si>
+    <t>(719) 542-2472</t>
+  </si>
+  <si>
+    <t>2025 US-50 #100, Pueblo, CO 81008</t>
+  </si>
+  <si>
+    <t>Saturday7:30 AM–1:30 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Smith+Brady+T+DDS/data=!4m7!3m6!1s0x8713a21ee42894fb:0x2f3d43fad3ebc999!8m2!3d38.3103831!4d-104.6338137!16s%2Fg%2F1wj_tqv5!19sChIJ-5Qo5B6iE4cRmcnr0_pDPS8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:36:34.652Z</t>
+  </si>
+  <si>
+    <t>Dr Andrea Schmidt DDS</t>
+  </si>
+  <si>
+    <t>(303) 544-9636</t>
+  </si>
+  <si>
+    <t>2495 Spruce St, Boulder, CO 80302</t>
+  </si>
+  <si>
+    <t>Boulder</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr+Andrea+Schmidt+DDS/data=!4m7!3m6!1s0x876bed7c33b62db5:0xe208c510aebd99aa!8m2!3d40.0225609!4d-105.2636193!16s%2Fg%2F11fsryk579!19sChIJtS22M3zta4cRqpm9rhDFCOI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:38:11.374Z</t>
+  </si>
+  <si>
+    <t>David Jackson, Dds</t>
+  </si>
+  <si>
+    <t>(303) 447-2872</t>
+  </si>
+  <si>
+    <t>3393 Iris Ave, Boulder, CO 80301</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/David+Jackson,+Dds/data=!4m7!3m6!1s0x876bee6e708100a1:0xf6dc04ec758cb86!8m2!3d40.0370105!4d-105.2492399!16s%2Fg%2F1tcwggkj!19sChIJoQCBcG7ua4cRhstYx07AbQ8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:38:54.799Z</t>
+  </si>
+  <si>
+    <t>Dr. Edward A. Christensen, DDS</t>
+  </si>
+  <si>
+    <t>(303) 604-9500</t>
+  </si>
+  <si>
+    <t>1140 W South Boulder Rd #102, Lafayette, CO 80026</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Edward+A.+Christensen,+DDS/data=!4m7!3m6!1s0x876bf494fe116ab1:0xa832d6f27451fde2!8m2!3d39.9865881!4d-105.1060703!16s%2Fg%2F1tjmf46z!19sChIJsWoR_pT0a4cR4v1RdPLWMqg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:39:34.226Z</t>
+  </si>
+  <si>
+    <t>Stacy Jackson</t>
+  </si>
+  <si>
+    <t>(303) 805-5703</t>
+  </si>
+  <si>
+    <t>3400 Penrose Pl Ste 107, Boulder, CO 80301</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Stacy+Jackson/data=!4m7!3m6!1s0x876c8e1131cabc47:0xa04341dc79fbbee7!8m2!3d40.0369027!4d-105.248352!16s%2Fg%2F11qgb73_yr!19sChIJR7zKMRGObIcR5777edxBQ6A?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:39:36.279Z</t>
+  </si>
+  <si>
+    <t>Dr. Alice Isom</t>
+  </si>
+  <si>
+    <t>(970) 744-4456</t>
+  </si>
+  <si>
+    <t>2855 35th Ave A, Greeley, CO 80634</t>
+  </si>
+  <si>
+    <t>Greeley</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Alice+Isom/data=!4m7!3m6!1s0x876ea139443aaaab:0xd9097f99a0c1fcfb!8m2!3d40.3888949!4d-104.7355507!16s%2Fg%2F11qgb6nxs4!19sChIJq6o6RDmhbocR-_zBoJl_Cdk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:42:07.476Z</t>
+  </si>
+  <si>
+    <t>Quick Dental Point</t>
+  </si>
+  <si>
+    <t>(970) 408-5693</t>
+  </si>
+  <si>
+    <t>814 8th St, Greeley, CO 80631</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Quick+Dental+Point/data=!4m7!3m6!1s0x876ea3e72859dc87:0xf5510a62b7e784b7!8m2!3d40.4245899!4d-104.6916273!16s%2Fg%2F11p1rflhsv!19sChIJh9xZKOejbocRt4Tnt2IKUfU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:42:24.901Z</t>
+  </si>
+  <si>
+    <t>Dr. Micah Pope</t>
+  </si>
+  <si>
+    <t>(970) 330-9900</t>
+  </si>
+  <si>
+    <t>2922 67th Ave Ste 102, Greeley, CO 80634</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Micah+Pope/data=!4m7!3m6!1s0x876ea69283700001:0xc42414b602757f45!8m2!3d40.3883145!4d-104.7867806!16s%2Fg%2F11kjq6wcm2!19sChIJAQBwg5KmbocRRX91ArYUJMQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:43:46.026Z</t>
+  </si>
+  <si>
+    <t>Dr. Lori Tima</t>
+  </si>
+  <si>
+    <t>(970) 330-5363</t>
+  </si>
+  <si>
+    <t>2021 Clubhouse Dr #110, Greeley, CO 80634</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Lori+Tima/data=!4m7!3m6!1s0x876ea6a6d9830215:0xeee75a28d8904aa2!8m2!3d40.4058584!4d-104.7686927!16s%2Fg%2F11tn6lz8dn!19sChIJFQKD2aambocRokqQ2Cha5-4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:44:10.228Z</t>
+  </si>
+  <si>
+    <t>Emergency Dentist Link</t>
+  </si>
+  <si>
+    <t>(970) 312-8544</t>
+  </si>
+  <si>
+    <t>3211 W 20th St, Greeley, CO 80634</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Emergency+Dentist+Link/data=!4m7!3m6!1s0x876ea195d12dd23b:0xb4068096cc0f846f!8m2!3d40.4067823!4d-104.7327772!16s%2Fg%2F11zzry1h8n!19sChIJO9It0ZWhbocRb4QPzJaABrQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:44:36.655Z</t>
   </si>
 </sst>
 </file>
@@ -490,7 +1870,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M3"/>
+  <dimension ref="A1:M82"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -630,6 +2010,3245 @@
         <v>32</v>
       </c>
     </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>33</v>
+      </c>
+      <c r="B4" t="s">
+        <v>34</v>
+      </c>
+      <c r="C4" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E4" t="s">
+        <v>17</v>
+      </c>
+      <c r="F4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G4" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I4" t="s">
+        <v>37</v>
+      </c>
+      <c r="J4" t="s">
+        <v>38</v>
+      </c>
+      <c r="K4" t="s">
+        <v>23</v>
+      </c>
+      <c r="L4" t="s">
+        <v>39</v>
+      </c>
+      <c r="M4" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C5" t="s">
+        <v>43</v>
+      </c>
+      <c r="D5" t="s">
+        <v>44</v>
+      </c>
+      <c r="E5" t="s">
+        <v>17</v>
+      </c>
+      <c r="F5" t="s">
+        <v>18</v>
+      </c>
+      <c r="G5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H5" t="s">
+        <v>20</v>
+      </c>
+      <c r="I5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" t="s">
+        <v>45</v>
+      </c>
+      <c r="K5" t="s">
+        <v>23</v>
+      </c>
+      <c r="L5" t="s">
+        <v>46</v>
+      </c>
+      <c r="M5" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>48</v>
+      </c>
+      <c r="B6" t="s">
+        <v>49</v>
+      </c>
+      <c r="C6" t="s">
+        <v>43</v>
+      </c>
+      <c r="D6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E6" t="s">
+        <v>17</v>
+      </c>
+      <c r="F6" t="s">
+        <v>18</v>
+      </c>
+      <c r="G6" t="s">
+        <v>19</v>
+      </c>
+      <c r="H6" t="s">
+        <v>20</v>
+      </c>
+      <c r="I6" t="s">
+        <v>21</v>
+      </c>
+      <c r="J6" t="s">
+        <v>45</v>
+      </c>
+      <c r="K6" t="s">
+        <v>23</v>
+      </c>
+      <c r="L6" t="s">
+        <v>51</v>
+      </c>
+      <c r="M6" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>53</v>
+      </c>
+      <c r="B7" t="s">
+        <v>54</v>
+      </c>
+      <c r="C7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7" t="s">
+        <v>55</v>
+      </c>
+      <c r="E7" t="s">
+        <v>17</v>
+      </c>
+      <c r="F7" t="s">
+        <v>18</v>
+      </c>
+      <c r="G7" t="s">
+        <v>19</v>
+      </c>
+      <c r="H7" t="s">
+        <v>29</v>
+      </c>
+      <c r="I7" t="s">
+        <v>21</v>
+      </c>
+      <c r="J7" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" t="s">
+        <v>23</v>
+      </c>
+      <c r="L7" t="s">
+        <v>56</v>
+      </c>
+      <c r="M7" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>58</v>
+      </c>
+      <c r="B8" t="s">
+        <v>59</v>
+      </c>
+      <c r="C8" t="s">
+        <v>60</v>
+      </c>
+      <c r="D8" t="s">
+        <v>61</v>
+      </c>
+      <c r="E8" t="s">
+        <v>17</v>
+      </c>
+      <c r="F8" t="s">
+        <v>18</v>
+      </c>
+      <c r="G8" t="s">
+        <v>19</v>
+      </c>
+      <c r="H8" t="s">
+        <v>20</v>
+      </c>
+      <c r="I8" t="s">
+        <v>21</v>
+      </c>
+      <c r="J8" t="s">
+        <v>62</v>
+      </c>
+      <c r="K8" t="s">
+        <v>23</v>
+      </c>
+      <c r="L8" t="s">
+        <v>63</v>
+      </c>
+      <c r="M8" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>65</v>
+      </c>
+      <c r="B9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D9" t="s">
+        <v>68</v>
+      </c>
+      <c r="E9" t="s">
+        <v>17</v>
+      </c>
+      <c r="F9" t="s">
+        <v>18</v>
+      </c>
+      <c r="G9" t="s">
+        <v>19</v>
+      </c>
+      <c r="H9" t="s">
+        <v>20</v>
+      </c>
+      <c r="I9" t="s">
+        <v>21</v>
+      </c>
+      <c r="J9" t="s">
+        <v>45</v>
+      </c>
+      <c r="K9" t="s">
+        <v>23</v>
+      </c>
+      <c r="L9" t="s">
+        <v>69</v>
+      </c>
+      <c r="M9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" t="s">
+        <v>60</v>
+      </c>
+      <c r="D10" t="s">
+        <v>73</v>
+      </c>
+      <c r="E10" t="s">
+        <v>74</v>
+      </c>
+      <c r="F10" t="s">
+        <v>18</v>
+      </c>
+      <c r="G10" t="s">
+        <v>19</v>
+      </c>
+      <c r="H10" t="s">
+        <v>75</v>
+      </c>
+      <c r="I10" t="s">
+        <v>21</v>
+      </c>
+      <c r="J10" t="s">
+        <v>22</v>
+      </c>
+      <c r="K10" t="s">
+        <v>23</v>
+      </c>
+      <c r="L10" t="s">
+        <v>76</v>
+      </c>
+      <c r="M10" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>78</v>
+      </c>
+      <c r="B11" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" t="s">
+        <v>81</v>
+      </c>
+      <c r="E11" t="s">
+        <v>74</v>
+      </c>
+      <c r="F11" t="s">
+        <v>18</v>
+      </c>
+      <c r="G11" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s">
+        <v>82</v>
+      </c>
+      <c r="I11" t="s">
+        <v>21</v>
+      </c>
+      <c r="J11" t="s">
+        <v>62</v>
+      </c>
+      <c r="K11" t="s">
+        <v>23</v>
+      </c>
+      <c r="L11" t="s">
+        <v>83</v>
+      </c>
+      <c r="M11" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>85</v>
+      </c>
+      <c r="B12" t="s">
+        <v>86</v>
+      </c>
+      <c r="C12" t="s">
+        <v>15</v>
+      </c>
+      <c r="D12" t="s">
+        <v>87</v>
+      </c>
+      <c r="E12" t="s">
+        <v>74</v>
+      </c>
+      <c r="F12" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" t="s">
+        <v>19</v>
+      </c>
+      <c r="H12" t="s">
+        <v>88</v>
+      </c>
+      <c r="I12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J12" t="s">
+        <v>22</v>
+      </c>
+      <c r="K12" t="s">
+        <v>23</v>
+      </c>
+      <c r="L12" t="s">
+        <v>89</v>
+      </c>
+      <c r="M12" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>91</v>
+      </c>
+      <c r="B13" t="s">
+        <v>92</v>
+      </c>
+      <c r="C13" t="s">
+        <v>15</v>
+      </c>
+      <c r="D13" t="s">
+        <v>93</v>
+      </c>
+      <c r="E13" t="s">
+        <v>74</v>
+      </c>
+      <c r="F13" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" t="s">
+        <v>19</v>
+      </c>
+      <c r="H13" t="s">
+        <v>94</v>
+      </c>
+      <c r="I13" t="s">
+        <v>21</v>
+      </c>
+      <c r="J13" t="s">
+        <v>22</v>
+      </c>
+      <c r="K13" t="s">
+        <v>23</v>
+      </c>
+      <c r="L13" t="s">
+        <v>95</v>
+      </c>
+      <c r="M13" t="s">
+        <v>96</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>97</v>
+      </c>
+      <c r="B14" t="s">
+        <v>98</v>
+      </c>
+      <c r="C14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D14" t="s">
+        <v>99</v>
+      </c>
+      <c r="E14" t="s">
+        <v>74</v>
+      </c>
+      <c r="F14" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" t="s">
+        <v>19</v>
+      </c>
+      <c r="H14" t="s">
+        <v>20</v>
+      </c>
+      <c r="I14" t="s">
+        <v>21</v>
+      </c>
+      <c r="J14" t="s">
+        <v>45</v>
+      </c>
+      <c r="K14" t="s">
+        <v>23</v>
+      </c>
+      <c r="L14" t="s">
+        <v>100</v>
+      </c>
+      <c r="M14" t="s">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>102</v>
+      </c>
+      <c r="B15" t="s">
+        <v>103</v>
+      </c>
+      <c r="C15" t="s">
+        <v>15</v>
+      </c>
+      <c r="D15" t="s">
+        <v>104</v>
+      </c>
+      <c r="E15" t="s">
+        <v>74</v>
+      </c>
+      <c r="F15" t="s">
+        <v>18</v>
+      </c>
+      <c r="G15" t="s">
+        <v>19</v>
+      </c>
+      <c r="H15" t="s">
+        <v>29</v>
+      </c>
+      <c r="I15" t="s">
+        <v>21</v>
+      </c>
+      <c r="J15" t="s">
+        <v>22</v>
+      </c>
+      <c r="K15" t="s">
+        <v>23</v>
+      </c>
+      <c r="L15" t="s">
+        <v>105</v>
+      </c>
+      <c r="M15" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>107</v>
+      </c>
+      <c r="B16" t="s">
+        <v>108</v>
+      </c>
+      <c r="C16" t="s">
+        <v>35</v>
+      </c>
+      <c r="D16" t="s">
+        <v>109</v>
+      </c>
+      <c r="E16" t="s">
+        <v>74</v>
+      </c>
+      <c r="F16" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" t="s">
+        <v>19</v>
+      </c>
+      <c r="H16" t="s">
+        <v>20</v>
+      </c>
+      <c r="I16" t="s">
+        <v>110</v>
+      </c>
+      <c r="J16" t="s">
+        <v>111</v>
+      </c>
+      <c r="K16" t="s">
+        <v>23</v>
+      </c>
+      <c r="L16" t="s">
+        <v>112</v>
+      </c>
+      <c r="M16" t="s">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>114</v>
+      </c>
+      <c r="B17" t="s">
+        <v>115</v>
+      </c>
+      <c r="C17" t="s">
+        <v>60</v>
+      </c>
+      <c r="D17" t="s">
+        <v>116</v>
+      </c>
+      <c r="E17" t="s">
+        <v>74</v>
+      </c>
+      <c r="F17" t="s">
+        <v>18</v>
+      </c>
+      <c r="G17" t="s">
+        <v>19</v>
+      </c>
+      <c r="H17" t="s">
+        <v>88</v>
+      </c>
+      <c r="I17" t="s">
+        <v>21</v>
+      </c>
+      <c r="J17" t="s">
+        <v>45</v>
+      </c>
+      <c r="K17" t="s">
+        <v>23</v>
+      </c>
+      <c r="L17" t="s">
+        <v>117</v>
+      </c>
+      <c r="M17" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>119</v>
+      </c>
+      <c r="B18" t="s">
+        <v>120</v>
+      </c>
+      <c r="C18" t="s">
+        <v>15</v>
+      </c>
+      <c r="D18" t="s">
+        <v>121</v>
+      </c>
+      <c r="E18" t="s">
+        <v>74</v>
+      </c>
+      <c r="F18" t="s">
+        <v>18</v>
+      </c>
+      <c r="G18" t="s">
+        <v>19</v>
+      </c>
+      <c r="H18" t="s">
+        <v>122</v>
+      </c>
+      <c r="I18" t="s">
+        <v>21</v>
+      </c>
+      <c r="J18" t="s">
+        <v>123</v>
+      </c>
+      <c r="K18" t="s">
+        <v>23</v>
+      </c>
+      <c r="L18" t="s">
+        <v>124</v>
+      </c>
+      <c r="M18" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>126</v>
+      </c>
+      <c r="B19" t="s">
+        <v>127</v>
+      </c>
+      <c r="C19" t="s">
+        <v>60</v>
+      </c>
+      <c r="D19" t="s">
+        <v>128</v>
+      </c>
+      <c r="E19" t="s">
+        <v>129</v>
+      </c>
+      <c r="F19" t="s">
+        <v>18</v>
+      </c>
+      <c r="G19" t="s">
+        <v>19</v>
+      </c>
+      <c r="H19" t="s">
+        <v>29</v>
+      </c>
+      <c r="I19" t="s">
+        <v>21</v>
+      </c>
+      <c r="J19" t="s">
+        <v>130</v>
+      </c>
+      <c r="K19" t="s">
+        <v>23</v>
+      </c>
+      <c r="L19" t="s">
+        <v>131</v>
+      </c>
+      <c r="M19" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>133</v>
+      </c>
+      <c r="B20" t="s">
+        <v>134</v>
+      </c>
+      <c r="C20" t="s">
+        <v>15</v>
+      </c>
+      <c r="D20" t="s">
+        <v>135</v>
+      </c>
+      <c r="E20" t="s">
+        <v>129</v>
+      </c>
+      <c r="F20" t="s">
+        <v>18</v>
+      </c>
+      <c r="G20" t="s">
+        <v>19</v>
+      </c>
+      <c r="H20" t="s">
+        <v>82</v>
+      </c>
+      <c r="I20" t="s">
+        <v>21</v>
+      </c>
+      <c r="J20" t="s">
+        <v>22</v>
+      </c>
+      <c r="K20" t="s">
+        <v>23</v>
+      </c>
+      <c r="L20" t="s">
+        <v>136</v>
+      </c>
+      <c r="M20" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>138</v>
+      </c>
+      <c r="B21" t="s">
+        <v>139</v>
+      </c>
+      <c r="C21" t="s">
+        <v>60</v>
+      </c>
+      <c r="D21" t="s">
+        <v>140</v>
+      </c>
+      <c r="E21" t="s">
+        <v>129</v>
+      </c>
+      <c r="F21" t="s">
+        <v>18</v>
+      </c>
+      <c r="G21" t="s">
+        <v>19</v>
+      </c>
+      <c r="H21" t="s">
+        <v>141</v>
+      </c>
+      <c r="I21" t="s">
+        <v>21</v>
+      </c>
+      <c r="J21" t="s">
+        <v>22</v>
+      </c>
+      <c r="K21" t="s">
+        <v>23</v>
+      </c>
+      <c r="L21" t="s">
+        <v>142</v>
+      </c>
+      <c r="M21" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>144</v>
+      </c>
+      <c r="B22" t="s">
+        <v>145</v>
+      </c>
+      <c r="C22" t="s">
+        <v>15</v>
+      </c>
+      <c r="D22" t="s">
+        <v>146</v>
+      </c>
+      <c r="E22" t="s">
+        <v>129</v>
+      </c>
+      <c r="F22" t="s">
+        <v>18</v>
+      </c>
+      <c r="G22" t="s">
+        <v>19</v>
+      </c>
+      <c r="H22" t="s">
+        <v>147</v>
+      </c>
+      <c r="I22" t="s">
+        <v>148</v>
+      </c>
+      <c r="J22" t="s">
+        <v>149</v>
+      </c>
+      <c r="K22" t="s">
+        <v>23</v>
+      </c>
+      <c r="L22" t="s">
+        <v>150</v>
+      </c>
+      <c r="M22" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>152</v>
+      </c>
+      <c r="B23" t="s">
+        <v>153</v>
+      </c>
+      <c r="C23" t="s">
+        <v>15</v>
+      </c>
+      <c r="D23" t="s">
+        <v>154</v>
+      </c>
+      <c r="E23" t="s">
+        <v>129</v>
+      </c>
+      <c r="F23" t="s">
+        <v>18</v>
+      </c>
+      <c r="G23" t="s">
+        <v>19</v>
+      </c>
+      <c r="H23" t="s">
+        <v>29</v>
+      </c>
+      <c r="I23" t="s">
+        <v>21</v>
+      </c>
+      <c r="J23" t="s">
+        <v>22</v>
+      </c>
+      <c r="K23" t="s">
+        <v>23</v>
+      </c>
+      <c r="L23" t="s">
+        <v>155</v>
+      </c>
+      <c r="M23" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>157</v>
+      </c>
+      <c r="B24" t="s">
+        <v>158</v>
+      </c>
+      <c r="C24" t="s">
+        <v>159</v>
+      </c>
+      <c r="D24" t="s">
+        <v>160</v>
+      </c>
+      <c r="E24" t="s">
+        <v>129</v>
+      </c>
+      <c r="F24" t="s">
+        <v>18</v>
+      </c>
+      <c r="G24" t="s">
+        <v>19</v>
+      </c>
+      <c r="H24" t="s">
+        <v>20</v>
+      </c>
+      <c r="I24" t="s">
+        <v>21</v>
+      </c>
+      <c r="J24" t="s">
+        <v>161</v>
+      </c>
+      <c r="K24" t="s">
+        <v>23</v>
+      </c>
+      <c r="L24" t="s">
+        <v>162</v>
+      </c>
+      <c r="M24" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>164</v>
+      </c>
+      <c r="B25" t="s">
+        <v>165</v>
+      </c>
+      <c r="C25" t="s">
+        <v>15</v>
+      </c>
+      <c r="D25" t="s">
+        <v>166</v>
+      </c>
+      <c r="E25" t="s">
+        <v>167</v>
+      </c>
+      <c r="F25" t="s">
+        <v>18</v>
+      </c>
+      <c r="G25" t="s">
+        <v>19</v>
+      </c>
+      <c r="H25" t="s">
+        <v>20</v>
+      </c>
+      <c r="I25" t="s">
+        <v>21</v>
+      </c>
+      <c r="J25" t="s">
+        <v>22</v>
+      </c>
+      <c r="K25" t="s">
+        <v>23</v>
+      </c>
+      <c r="L25" t="s">
+        <v>168</v>
+      </c>
+      <c r="M25" t="s">
+        <v>169</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>170</v>
+      </c>
+      <c r="B26" t="s">
+        <v>171</v>
+      </c>
+      <c r="C26" t="s">
+        <v>159</v>
+      </c>
+      <c r="D26" t="s">
+        <v>172</v>
+      </c>
+      <c r="E26" t="s">
+        <v>167</v>
+      </c>
+      <c r="F26" t="s">
+        <v>18</v>
+      </c>
+      <c r="G26" t="s">
+        <v>19</v>
+      </c>
+      <c r="H26" t="s">
+        <v>173</v>
+      </c>
+      <c r="I26" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" t="s">
+        <v>45</v>
+      </c>
+      <c r="K26" t="s">
+        <v>23</v>
+      </c>
+      <c r="L26" t="s">
+        <v>174</v>
+      </c>
+      <c r="M26" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A27" t="s">
+        <v>176</v>
+      </c>
+      <c r="B27" t="s">
+        <v>177</v>
+      </c>
+      <c r="C27" t="s">
+        <v>15</v>
+      </c>
+      <c r="D27" t="s">
+        <v>178</v>
+      </c>
+      <c r="E27" t="s">
+        <v>167</v>
+      </c>
+      <c r="F27" t="s">
+        <v>18</v>
+      </c>
+      <c r="G27" t="s">
+        <v>19</v>
+      </c>
+      <c r="H27" t="s">
+        <v>45</v>
+      </c>
+      <c r="I27" t="s">
+        <v>179</v>
+      </c>
+      <c r="J27" t="s">
+        <v>45</v>
+      </c>
+      <c r="K27" t="s">
+        <v>23</v>
+      </c>
+      <c r="L27" t="s">
+        <v>180</v>
+      </c>
+      <c r="M27" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>182</v>
+      </c>
+      <c r="B28" t="s">
+        <v>183</v>
+      </c>
+      <c r="C28" t="s">
+        <v>43</v>
+      </c>
+      <c r="D28" t="s">
+        <v>184</v>
+      </c>
+      <c r="E28" t="s">
+        <v>167</v>
+      </c>
+      <c r="F28" t="s">
+        <v>18</v>
+      </c>
+      <c r="G28" t="s">
+        <v>19</v>
+      </c>
+      <c r="H28" t="s">
+        <v>45</v>
+      </c>
+      <c r="I28" t="s">
+        <v>179</v>
+      </c>
+      <c r="J28" t="s">
+        <v>45</v>
+      </c>
+      <c r="K28" t="s">
+        <v>23</v>
+      </c>
+      <c r="L28" t="s">
+        <v>185</v>
+      </c>
+      <c r="M28" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A29" t="s">
+        <v>187</v>
+      </c>
+      <c r="B29" t="s">
+        <v>188</v>
+      </c>
+      <c r="C29" t="s">
+        <v>43</v>
+      </c>
+      <c r="D29" t="s">
+        <v>189</v>
+      </c>
+      <c r="E29" t="s">
+        <v>167</v>
+      </c>
+      <c r="F29" t="s">
+        <v>18</v>
+      </c>
+      <c r="G29" t="s">
+        <v>19</v>
+      </c>
+      <c r="H29" t="s">
+        <v>190</v>
+      </c>
+      <c r="I29" t="s">
+        <v>21</v>
+      </c>
+      <c r="J29" t="s">
+        <v>45</v>
+      </c>
+      <c r="K29" t="s">
+        <v>23</v>
+      </c>
+      <c r="L29" t="s">
+        <v>191</v>
+      </c>
+      <c r="M29" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A30" t="s">
+        <v>193</v>
+      </c>
+      <c r="B30" t="s">
+        <v>194</v>
+      </c>
+      <c r="C30" t="s">
+        <v>43</v>
+      </c>
+      <c r="D30" t="s">
+        <v>195</v>
+      </c>
+      <c r="E30" t="s">
+        <v>196</v>
+      </c>
+      <c r="F30" t="s">
+        <v>18</v>
+      </c>
+      <c r="G30" t="s">
+        <v>19</v>
+      </c>
+      <c r="H30" t="s">
+        <v>45</v>
+      </c>
+      <c r="I30" t="s">
+        <v>179</v>
+      </c>
+      <c r="J30" t="s">
+        <v>45</v>
+      </c>
+      <c r="K30" t="s">
+        <v>23</v>
+      </c>
+      <c r="L30" t="s">
+        <v>197</v>
+      </c>
+      <c r="M30" t="s">
+        <v>198</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A31" t="s">
+        <v>199</v>
+      </c>
+      <c r="B31" t="s">
+        <v>200</v>
+      </c>
+      <c r="C31" t="s">
+        <v>43</v>
+      </c>
+      <c r="D31" t="s">
+        <v>201</v>
+      </c>
+      <c r="E31" t="s">
+        <v>167</v>
+      </c>
+      <c r="F31" t="s">
+        <v>18</v>
+      </c>
+      <c r="G31" t="s">
+        <v>19</v>
+      </c>
+      <c r="H31" t="s">
+        <v>45</v>
+      </c>
+      <c r="I31" t="s">
+        <v>179</v>
+      </c>
+      <c r="J31" t="s">
+        <v>45</v>
+      </c>
+      <c r="K31" t="s">
+        <v>23</v>
+      </c>
+      <c r="L31" t="s">
+        <v>202</v>
+      </c>
+      <c r="M31" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A32" t="s">
+        <v>204</v>
+      </c>
+      <c r="B32" t="s">
+        <v>205</v>
+      </c>
+      <c r="C32" t="s">
+        <v>35</v>
+      </c>
+      <c r="D32" t="s">
+        <v>206</v>
+      </c>
+      <c r="E32" t="s">
+        <v>167</v>
+      </c>
+      <c r="F32" t="s">
+        <v>18</v>
+      </c>
+      <c r="G32" t="s">
+        <v>19</v>
+      </c>
+      <c r="H32" t="s">
+        <v>45</v>
+      </c>
+      <c r="I32" t="s">
+        <v>207</v>
+      </c>
+      <c r="J32" t="s">
+        <v>45</v>
+      </c>
+      <c r="K32" t="s">
+        <v>23</v>
+      </c>
+      <c r="L32" t="s">
+        <v>208</v>
+      </c>
+      <c r="M32" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A33" t="s">
+        <v>210</v>
+      </c>
+      <c r="B33" t="s">
+        <v>211</v>
+      </c>
+      <c r="C33" t="s">
+        <v>212</v>
+      </c>
+      <c r="D33" t="s">
+        <v>213</v>
+      </c>
+      <c r="E33" t="s">
+        <v>214</v>
+      </c>
+      <c r="F33" t="s">
+        <v>18</v>
+      </c>
+      <c r="G33" t="s">
+        <v>19</v>
+      </c>
+      <c r="H33" t="s">
+        <v>215</v>
+      </c>
+      <c r="I33" t="s">
+        <v>216</v>
+      </c>
+      <c r="J33" t="s">
+        <v>217</v>
+      </c>
+      <c r="K33" t="s">
+        <v>23</v>
+      </c>
+      <c r="L33" t="s">
+        <v>218</v>
+      </c>
+      <c r="M33" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A34" t="s">
+        <v>220</v>
+      </c>
+      <c r="B34" t="s">
+        <v>221</v>
+      </c>
+      <c r="C34" t="s">
+        <v>15</v>
+      </c>
+      <c r="D34" t="s">
+        <v>222</v>
+      </c>
+      <c r="E34" t="s">
+        <v>214</v>
+      </c>
+      <c r="F34" t="s">
+        <v>18</v>
+      </c>
+      <c r="G34" t="s">
+        <v>19</v>
+      </c>
+      <c r="H34" t="s">
+        <v>223</v>
+      </c>
+      <c r="I34" t="s">
+        <v>21</v>
+      </c>
+      <c r="J34" t="s">
+        <v>22</v>
+      </c>
+      <c r="K34" t="s">
+        <v>23</v>
+      </c>
+      <c r="L34" t="s">
+        <v>224</v>
+      </c>
+      <c r="M34" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>226</v>
+      </c>
+      <c r="B35" t="s">
+        <v>227</v>
+      </c>
+      <c r="C35" t="s">
+        <v>15</v>
+      </c>
+      <c r="D35" t="s">
+        <v>228</v>
+      </c>
+      <c r="E35" t="s">
+        <v>214</v>
+      </c>
+      <c r="F35" t="s">
+        <v>18</v>
+      </c>
+      <c r="G35" t="s">
+        <v>19</v>
+      </c>
+      <c r="H35" t="s">
+        <v>45</v>
+      </c>
+      <c r="I35" t="s">
+        <v>179</v>
+      </c>
+      <c r="J35" t="s">
+        <v>22</v>
+      </c>
+      <c r="K35" t="s">
+        <v>23</v>
+      </c>
+      <c r="L35" t="s">
+        <v>229</v>
+      </c>
+      <c r="M35" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A36" t="s">
+        <v>231</v>
+      </c>
+      <c r="B36" t="s">
+        <v>232</v>
+      </c>
+      <c r="C36" t="s">
+        <v>43</v>
+      </c>
+      <c r="D36" t="s">
+        <v>233</v>
+      </c>
+      <c r="E36" t="s">
+        <v>214</v>
+      </c>
+      <c r="F36" t="s">
+        <v>18</v>
+      </c>
+      <c r="G36" t="s">
+        <v>19</v>
+      </c>
+      <c r="H36" t="s">
+        <v>45</v>
+      </c>
+      <c r="I36" t="s">
+        <v>179</v>
+      </c>
+      <c r="J36" t="s">
+        <v>45</v>
+      </c>
+      <c r="K36" t="s">
+        <v>23</v>
+      </c>
+      <c r="L36" t="s">
+        <v>234</v>
+      </c>
+      <c r="M36" t="s">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>236</v>
+      </c>
+      <c r="B37" t="s">
+        <v>237</v>
+      </c>
+      <c r="C37" t="s">
+        <v>60</v>
+      </c>
+      <c r="D37" t="s">
+        <v>238</v>
+      </c>
+      <c r="E37" t="s">
+        <v>239</v>
+      </c>
+      <c r="F37" t="s">
+        <v>18</v>
+      </c>
+      <c r="G37" t="s">
+        <v>19</v>
+      </c>
+      <c r="H37" t="s">
+        <v>45</v>
+      </c>
+      <c r="I37" t="s">
+        <v>179</v>
+      </c>
+      <c r="J37" t="s">
+        <v>45</v>
+      </c>
+      <c r="K37" t="s">
+        <v>23</v>
+      </c>
+      <c r="L37" t="s">
+        <v>240</v>
+      </c>
+      <c r="M37" t="s">
+        <v>241</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A38" t="s">
+        <v>242</v>
+      </c>
+      <c r="B38" t="s">
+        <v>243</v>
+      </c>
+      <c r="C38" t="s">
+        <v>43</v>
+      </c>
+      <c r="D38" t="s">
+        <v>244</v>
+      </c>
+      <c r="E38" t="s">
+        <v>245</v>
+      </c>
+      <c r="F38" t="s">
+        <v>18</v>
+      </c>
+      <c r="G38" t="s">
+        <v>19</v>
+      </c>
+      <c r="H38" t="s">
+        <v>45</v>
+      </c>
+      <c r="I38" t="s">
+        <v>179</v>
+      </c>
+      <c r="J38" t="s">
+        <v>45</v>
+      </c>
+      <c r="K38" t="s">
+        <v>23</v>
+      </c>
+      <c r="L38" t="s">
+        <v>246</v>
+      </c>
+      <c r="M38" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A39" t="s">
+        <v>248</v>
+      </c>
+      <c r="B39" t="s">
+        <v>249</v>
+      </c>
+      <c r="C39" t="s">
+        <v>35</v>
+      </c>
+      <c r="D39" t="s">
+        <v>250</v>
+      </c>
+      <c r="E39" t="s">
+        <v>251</v>
+      </c>
+      <c r="F39" t="s">
+        <v>18</v>
+      </c>
+      <c r="G39" t="s">
+        <v>19</v>
+      </c>
+      <c r="H39" t="s">
+        <v>20</v>
+      </c>
+      <c r="I39" t="s">
+        <v>37</v>
+      </c>
+      <c r="J39" t="s">
+        <v>45</v>
+      </c>
+      <c r="K39" t="s">
+        <v>23</v>
+      </c>
+      <c r="L39" t="s">
+        <v>252</v>
+      </c>
+      <c r="M39" t="s">
+        <v>253</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A40" t="s">
+        <v>254</v>
+      </c>
+      <c r="B40" t="s">
+        <v>255</v>
+      </c>
+      <c r="C40" t="s">
+        <v>35</v>
+      </c>
+      <c r="D40" t="s">
+        <v>256</v>
+      </c>
+      <c r="E40" t="s">
+        <v>257</v>
+      </c>
+      <c r="F40" t="s">
+        <v>18</v>
+      </c>
+      <c r="G40" t="s">
+        <v>19</v>
+      </c>
+      <c r="H40" t="s">
+        <v>75</v>
+      </c>
+      <c r="I40" t="s">
+        <v>258</v>
+      </c>
+      <c r="J40" t="s">
+        <v>45</v>
+      </c>
+      <c r="K40" t="s">
+        <v>23</v>
+      </c>
+      <c r="L40" t="s">
+        <v>259</v>
+      </c>
+      <c r="M40" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>261</v>
+      </c>
+      <c r="B41" t="s">
+        <v>262</v>
+      </c>
+      <c r="C41" t="s">
+        <v>15</v>
+      </c>
+      <c r="D41" t="s">
+        <v>263</v>
+      </c>
+      <c r="E41" t="s">
+        <v>239</v>
+      </c>
+      <c r="F41" t="s">
+        <v>18</v>
+      </c>
+      <c r="G41" t="s">
+        <v>19</v>
+      </c>
+      <c r="H41" t="s">
+        <v>20</v>
+      </c>
+      <c r="I41" t="s">
+        <v>21</v>
+      </c>
+      <c r="J41" t="s">
+        <v>22</v>
+      </c>
+      <c r="K41" t="s">
+        <v>23</v>
+      </c>
+      <c r="L41" t="s">
+        <v>264</v>
+      </c>
+      <c r="M41" t="s">
+        <v>265</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>266</v>
+      </c>
+      <c r="B42" t="s">
+        <v>267</v>
+      </c>
+      <c r="C42" t="s">
+        <v>15</v>
+      </c>
+      <c r="D42" t="s">
+        <v>268</v>
+      </c>
+      <c r="E42" t="s">
+        <v>239</v>
+      </c>
+      <c r="F42" t="s">
+        <v>18</v>
+      </c>
+      <c r="G42" t="s">
+        <v>19</v>
+      </c>
+      <c r="H42" t="s">
+        <v>20</v>
+      </c>
+      <c r="I42" t="s">
+        <v>21</v>
+      </c>
+      <c r="J42" t="s">
+        <v>45</v>
+      </c>
+      <c r="K42" t="s">
+        <v>23</v>
+      </c>
+      <c r="L42" t="s">
+        <v>269</v>
+      </c>
+      <c r="M42" t="s">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A43" t="s">
+        <v>271</v>
+      </c>
+      <c r="B43" t="s">
+        <v>272</v>
+      </c>
+      <c r="C43" t="s">
+        <v>15</v>
+      </c>
+      <c r="D43" t="s">
+        <v>273</v>
+      </c>
+      <c r="E43" t="s">
+        <v>274</v>
+      </c>
+      <c r="F43" t="s">
+        <v>18</v>
+      </c>
+      <c r="G43" t="s">
+        <v>19</v>
+      </c>
+      <c r="H43" t="s">
+        <v>29</v>
+      </c>
+      <c r="I43" t="s">
+        <v>21</v>
+      </c>
+      <c r="J43" t="s">
+        <v>22</v>
+      </c>
+      <c r="K43" t="s">
+        <v>23</v>
+      </c>
+      <c r="L43" t="s">
+        <v>275</v>
+      </c>
+      <c r="M43" t="s">
+        <v>276</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A44" t="s">
+        <v>277</v>
+      </c>
+      <c r="B44" t="s">
+        <v>278</v>
+      </c>
+      <c r="C44" t="s">
+        <v>15</v>
+      </c>
+      <c r="D44" t="s">
+        <v>279</v>
+      </c>
+      <c r="E44" t="s">
+        <v>274</v>
+      </c>
+      <c r="F44" t="s">
+        <v>18</v>
+      </c>
+      <c r="G44" t="s">
+        <v>19</v>
+      </c>
+      <c r="H44" t="s">
+        <v>20</v>
+      </c>
+      <c r="I44" t="s">
+        <v>21</v>
+      </c>
+      <c r="J44" t="s">
+        <v>22</v>
+      </c>
+      <c r="K44" t="s">
+        <v>23</v>
+      </c>
+      <c r="L44" t="s">
+        <v>280</v>
+      </c>
+      <c r="M44" t="s">
+        <v>281</v>
+      </c>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>282</v>
+      </c>
+      <c r="B45" t="s">
+        <v>283</v>
+      </c>
+      <c r="C45" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" t="s">
+        <v>284</v>
+      </c>
+      <c r="E45" t="s">
+        <v>274</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H45" t="s">
+        <v>94</v>
+      </c>
+      <c r="I45" t="s">
+        <v>21</v>
+      </c>
+      <c r="J45" t="s">
+        <v>45</v>
+      </c>
+      <c r="K45" t="s">
+        <v>23</v>
+      </c>
+      <c r="L45" t="s">
+        <v>285</v>
+      </c>
+      <c r="M45" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>287</v>
+      </c>
+      <c r="B46" t="s">
+        <v>288</v>
+      </c>
+      <c r="C46" t="s">
+        <v>289</v>
+      </c>
+      <c r="D46" t="s">
+        <v>290</v>
+      </c>
+      <c r="E46" t="s">
+        <v>274</v>
+      </c>
+      <c r="F46" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" t="s">
+        <v>19</v>
+      </c>
+      <c r="H46" t="s">
+        <v>291</v>
+      </c>
+      <c r="I46" t="s">
+        <v>21</v>
+      </c>
+      <c r="J46" t="s">
+        <v>292</v>
+      </c>
+      <c r="K46" t="s">
+        <v>23</v>
+      </c>
+      <c r="L46" t="s">
+        <v>293</v>
+      </c>
+      <c r="M46" t="s">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>295</v>
+      </c>
+      <c r="B47" t="s">
+        <v>296</v>
+      </c>
+      <c r="C47" t="s">
+        <v>297</v>
+      </c>
+      <c r="D47" t="s">
+        <v>298</v>
+      </c>
+      <c r="E47" t="s">
+        <v>274</v>
+      </c>
+      <c r="F47" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" t="s">
+        <v>19</v>
+      </c>
+      <c r="H47" t="s">
+        <v>190</v>
+      </c>
+      <c r="I47" t="s">
+        <v>21</v>
+      </c>
+      <c r="J47" t="s">
+        <v>22</v>
+      </c>
+      <c r="K47" t="s">
+        <v>23</v>
+      </c>
+      <c r="L47" t="s">
+        <v>299</v>
+      </c>
+      <c r="M47" t="s">
+        <v>300</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>301</v>
+      </c>
+      <c r="B48" t="s">
+        <v>302</v>
+      </c>
+      <c r="C48" t="s">
+        <v>43</v>
+      </c>
+      <c r="D48" t="s">
+        <v>303</v>
+      </c>
+      <c r="E48" t="s">
+        <v>274</v>
+      </c>
+      <c r="F48" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" t="s">
+        <v>19</v>
+      </c>
+      <c r="H48" t="s">
+        <v>20</v>
+      </c>
+      <c r="I48" t="s">
+        <v>21</v>
+      </c>
+      <c r="J48" t="s">
+        <v>45</v>
+      </c>
+      <c r="K48" t="s">
+        <v>23</v>
+      </c>
+      <c r="L48" t="s">
+        <v>304</v>
+      </c>
+      <c r="M48" t="s">
+        <v>305</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>306</v>
+      </c>
+      <c r="B49" t="s">
+        <v>307</v>
+      </c>
+      <c r="C49" t="s">
+        <v>67</v>
+      </c>
+      <c r="D49" t="s">
+        <v>308</v>
+      </c>
+      <c r="E49" t="s">
+        <v>274</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" t="s">
+        <v>19</v>
+      </c>
+      <c r="H49" t="s">
+        <v>173</v>
+      </c>
+      <c r="I49" t="s">
+        <v>21</v>
+      </c>
+      <c r="J49" t="s">
+        <v>123</v>
+      </c>
+      <c r="K49" t="s">
+        <v>23</v>
+      </c>
+      <c r="L49" t="s">
+        <v>309</v>
+      </c>
+      <c r="M49" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>311</v>
+      </c>
+      <c r="B50" t="s">
+        <v>312</v>
+      </c>
+      <c r="C50" t="s">
+        <v>60</v>
+      </c>
+      <c r="D50" t="s">
+        <v>313</v>
+      </c>
+      <c r="E50" t="s">
+        <v>314</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" t="s">
+        <v>19</v>
+      </c>
+      <c r="H50" t="s">
+        <v>291</v>
+      </c>
+      <c r="I50" t="s">
+        <v>21</v>
+      </c>
+      <c r="J50" t="s">
+        <v>22</v>
+      </c>
+      <c r="K50" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" t="s">
+        <v>315</v>
+      </c>
+      <c r="M50" t="s">
+        <v>316</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>317</v>
+      </c>
+      <c r="B51" t="s">
+        <v>318</v>
+      </c>
+      <c r="C51" t="s">
+        <v>319</v>
+      </c>
+      <c r="D51" t="s">
+        <v>320</v>
+      </c>
+      <c r="E51" t="s">
+        <v>274</v>
+      </c>
+      <c r="F51" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" t="s">
+        <v>19</v>
+      </c>
+      <c r="H51" t="s">
+        <v>45</v>
+      </c>
+      <c r="I51" t="s">
+        <v>179</v>
+      </c>
+      <c r="J51" t="s">
+        <v>45</v>
+      </c>
+      <c r="K51" t="s">
+        <v>23</v>
+      </c>
+      <c r="L51" t="s">
+        <v>321</v>
+      </c>
+      <c r="M51" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>323</v>
+      </c>
+      <c r="B52" t="s">
+        <v>324</v>
+      </c>
+      <c r="C52" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" t="s">
+        <v>325</v>
+      </c>
+      <c r="E52" t="s">
+        <v>274</v>
+      </c>
+      <c r="F52" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" t="s">
+        <v>19</v>
+      </c>
+      <c r="H52" t="s">
+        <v>45</v>
+      </c>
+      <c r="I52" t="s">
+        <v>179</v>
+      </c>
+      <c r="J52" t="s">
+        <v>45</v>
+      </c>
+      <c r="K52" t="s">
+        <v>23</v>
+      </c>
+      <c r="L52" t="s">
+        <v>326</v>
+      </c>
+      <c r="M52" t="s">
+        <v>327</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>328</v>
+      </c>
+      <c r="B53" t="s">
+        <v>329</v>
+      </c>
+      <c r="C53" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" t="s">
+        <v>330</v>
+      </c>
+      <c r="E53" t="s">
+        <v>331</v>
+      </c>
+      <c r="F53" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" t="s">
+        <v>19</v>
+      </c>
+      <c r="H53" t="s">
+        <v>88</v>
+      </c>
+      <c r="I53" t="s">
+        <v>21</v>
+      </c>
+      <c r="J53" t="s">
+        <v>22</v>
+      </c>
+      <c r="K53" t="s">
+        <v>23</v>
+      </c>
+      <c r="L53" t="s">
+        <v>332</v>
+      </c>
+      <c r="M53" t="s">
+        <v>333</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>334</v>
+      </c>
+      <c r="B54" t="s">
+        <v>335</v>
+      </c>
+      <c r="C54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D54" t="s">
+        <v>336</v>
+      </c>
+      <c r="E54" t="s">
+        <v>331</v>
+      </c>
+      <c r="F54" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" t="s">
+        <v>19</v>
+      </c>
+      <c r="H54" t="s">
+        <v>291</v>
+      </c>
+      <c r="I54" t="s">
+        <v>21</v>
+      </c>
+      <c r="J54" t="s">
+        <v>22</v>
+      </c>
+      <c r="K54" t="s">
+        <v>23</v>
+      </c>
+      <c r="L54" t="s">
+        <v>337</v>
+      </c>
+      <c r="M54" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>339</v>
+      </c>
+      <c r="B55" t="s">
+        <v>340</v>
+      </c>
+      <c r="C55" t="s">
+        <v>15</v>
+      </c>
+      <c r="D55" t="s">
+        <v>341</v>
+      </c>
+      <c r="E55" t="s">
+        <v>257</v>
+      </c>
+      <c r="F55" t="s">
+        <v>18</v>
+      </c>
+      <c r="G55" t="s">
+        <v>19</v>
+      </c>
+      <c r="H55" t="s">
+        <v>88</v>
+      </c>
+      <c r="I55" t="s">
+        <v>21</v>
+      </c>
+      <c r="J55" t="s">
+        <v>45</v>
+      </c>
+      <c r="K55" t="s">
+        <v>23</v>
+      </c>
+      <c r="L55" t="s">
+        <v>342</v>
+      </c>
+      <c r="M55" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>344</v>
+      </c>
+      <c r="B56" t="s">
+        <v>345</v>
+      </c>
+      <c r="C56" t="s">
+        <v>43</v>
+      </c>
+      <c r="D56" t="s">
+        <v>346</v>
+      </c>
+      <c r="E56" t="s">
+        <v>331</v>
+      </c>
+      <c r="F56" t="s">
+        <v>18</v>
+      </c>
+      <c r="G56" t="s">
+        <v>19</v>
+      </c>
+      <c r="H56" t="s">
+        <v>20</v>
+      </c>
+      <c r="I56" t="s">
+        <v>21</v>
+      </c>
+      <c r="J56" t="s">
+        <v>45</v>
+      </c>
+      <c r="K56" t="s">
+        <v>23</v>
+      </c>
+      <c r="L56" t="s">
+        <v>347</v>
+      </c>
+      <c r="M56" t="s">
+        <v>348</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>349</v>
+      </c>
+      <c r="B57" t="s">
+        <v>350</v>
+      </c>
+      <c r="C57" t="s">
+        <v>43</v>
+      </c>
+      <c r="D57" t="s">
+        <v>351</v>
+      </c>
+      <c r="E57" t="s">
+        <v>352</v>
+      </c>
+      <c r="F57" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" t="s">
+        <v>19</v>
+      </c>
+      <c r="H57" t="s">
+        <v>45</v>
+      </c>
+      <c r="I57" t="s">
+        <v>179</v>
+      </c>
+      <c r="J57" t="s">
+        <v>45</v>
+      </c>
+      <c r="K57" t="s">
+        <v>23</v>
+      </c>
+      <c r="L57" t="s">
+        <v>353</v>
+      </c>
+      <c r="M57" t="s">
+        <v>354</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>355</v>
+      </c>
+      <c r="B58" t="s">
+        <v>356</v>
+      </c>
+      <c r="C58" t="s">
+        <v>15</v>
+      </c>
+      <c r="D58" t="s">
+        <v>357</v>
+      </c>
+      <c r="E58" t="s">
+        <v>331</v>
+      </c>
+      <c r="F58" t="s">
+        <v>18</v>
+      </c>
+      <c r="G58" t="s">
+        <v>19</v>
+      </c>
+      <c r="H58" t="s">
+        <v>45</v>
+      </c>
+      <c r="I58" t="s">
+        <v>179</v>
+      </c>
+      <c r="J58" t="s">
+        <v>45</v>
+      </c>
+      <c r="K58" t="s">
+        <v>23</v>
+      </c>
+      <c r="L58" t="s">
+        <v>358</v>
+      </c>
+      <c r="M58" t="s">
+        <v>359</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>360</v>
+      </c>
+      <c r="B59" t="s">
+        <v>361</v>
+      </c>
+      <c r="C59" t="s">
+        <v>15</v>
+      </c>
+      <c r="D59" t="s">
+        <v>362</v>
+      </c>
+      <c r="E59" t="s">
+        <v>363</v>
+      </c>
+      <c r="F59" t="s">
+        <v>18</v>
+      </c>
+      <c r="G59" t="s">
+        <v>19</v>
+      </c>
+      <c r="H59" t="s">
+        <v>215</v>
+      </c>
+      <c r="I59" t="s">
+        <v>21</v>
+      </c>
+      <c r="J59" t="s">
+        <v>22</v>
+      </c>
+      <c r="K59" t="s">
+        <v>23</v>
+      </c>
+      <c r="L59" t="s">
+        <v>364</v>
+      </c>
+      <c r="M59" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>366</v>
+      </c>
+      <c r="B60" t="s">
+        <v>367</v>
+      </c>
+      <c r="C60" t="s">
+        <v>60</v>
+      </c>
+      <c r="D60" t="s">
+        <v>368</v>
+      </c>
+      <c r="E60" t="s">
+        <v>363</v>
+      </c>
+      <c r="F60" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60" t="s">
+        <v>19</v>
+      </c>
+      <c r="H60" t="s">
+        <v>45</v>
+      </c>
+      <c r="I60" t="s">
+        <v>179</v>
+      </c>
+      <c r="J60" t="s">
+        <v>62</v>
+      </c>
+      <c r="K60" t="s">
+        <v>23</v>
+      </c>
+      <c r="L60" t="s">
+        <v>369</v>
+      </c>
+      <c r="M60" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>371</v>
+      </c>
+      <c r="B61" t="s">
+        <v>372</v>
+      </c>
+      <c r="C61" t="s">
+        <v>60</v>
+      </c>
+      <c r="D61" t="s">
+        <v>373</v>
+      </c>
+      <c r="E61" t="s">
+        <v>363</v>
+      </c>
+      <c r="F61" t="s">
+        <v>18</v>
+      </c>
+      <c r="G61" t="s">
+        <v>19</v>
+      </c>
+      <c r="H61" t="s">
+        <v>374</v>
+      </c>
+      <c r="I61" t="s">
+        <v>21</v>
+      </c>
+      <c r="J61" t="s">
+        <v>22</v>
+      </c>
+      <c r="K61" t="s">
+        <v>23</v>
+      </c>
+      <c r="L61" t="s">
+        <v>375</v>
+      </c>
+      <c r="M61" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>377</v>
+      </c>
+      <c r="B62" t="s">
+        <v>378</v>
+      </c>
+      <c r="C62" t="s">
+        <v>60</v>
+      </c>
+      <c r="D62" t="s">
+        <v>379</v>
+      </c>
+      <c r="E62" t="s">
+        <v>363</v>
+      </c>
+      <c r="F62" t="s">
+        <v>18</v>
+      </c>
+      <c r="G62" t="s">
+        <v>19</v>
+      </c>
+      <c r="H62" t="s">
+        <v>45</v>
+      </c>
+      <c r="I62" t="s">
+        <v>179</v>
+      </c>
+      <c r="J62" t="s">
+        <v>380</v>
+      </c>
+      <c r="K62" t="s">
+        <v>23</v>
+      </c>
+      <c r="L62" t="s">
+        <v>381</v>
+      </c>
+      <c r="M62" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>383</v>
+      </c>
+      <c r="B63" t="s">
+        <v>384</v>
+      </c>
+      <c r="C63" t="s">
+        <v>60</v>
+      </c>
+      <c r="D63" t="s">
+        <v>385</v>
+      </c>
+      <c r="E63" t="s">
+        <v>363</v>
+      </c>
+      <c r="F63" t="s">
+        <v>18</v>
+      </c>
+      <c r="G63" t="s">
+        <v>19</v>
+      </c>
+      <c r="H63" t="s">
+        <v>20</v>
+      </c>
+      <c r="I63" t="s">
+        <v>21</v>
+      </c>
+      <c r="J63" t="s">
+        <v>22</v>
+      </c>
+      <c r="K63" t="s">
+        <v>23</v>
+      </c>
+      <c r="L63" t="s">
+        <v>386</v>
+      </c>
+      <c r="M63" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>388</v>
+      </c>
+      <c r="B64" t="s">
+        <v>389</v>
+      </c>
+      <c r="C64" t="s">
+        <v>80</v>
+      </c>
+      <c r="D64" t="s">
+        <v>390</v>
+      </c>
+      <c r="E64" t="s">
+        <v>363</v>
+      </c>
+      <c r="F64" t="s">
+        <v>18</v>
+      </c>
+      <c r="G64" t="s">
+        <v>19</v>
+      </c>
+      <c r="H64" t="s">
+        <v>45</v>
+      </c>
+      <c r="I64" t="s">
+        <v>179</v>
+      </c>
+      <c r="J64" t="s">
+        <v>45</v>
+      </c>
+      <c r="K64" t="s">
+        <v>23</v>
+      </c>
+      <c r="L64" t="s">
+        <v>391</v>
+      </c>
+      <c r="M64" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>393</v>
+      </c>
+      <c r="B65" t="s">
+        <v>394</v>
+      </c>
+      <c r="C65" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65" t="s">
+        <v>395</v>
+      </c>
+      <c r="E65" t="s">
+        <v>363</v>
+      </c>
+      <c r="F65" t="s">
+        <v>18</v>
+      </c>
+      <c r="G65" t="s">
+        <v>19</v>
+      </c>
+      <c r="H65" t="s">
+        <v>215</v>
+      </c>
+      <c r="I65" t="s">
+        <v>21</v>
+      </c>
+      <c r="J65" t="s">
+        <v>22</v>
+      </c>
+      <c r="K65" t="s">
+        <v>23</v>
+      </c>
+      <c r="L65" t="s">
+        <v>396</v>
+      </c>
+      <c r="M65" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>398</v>
+      </c>
+      <c r="B66" t="s">
+        <v>399</v>
+      </c>
+      <c r="C66" t="s">
+        <v>15</v>
+      </c>
+      <c r="D66" t="s">
+        <v>400</v>
+      </c>
+      <c r="E66" t="s">
+        <v>363</v>
+      </c>
+      <c r="F66" t="s">
+        <v>18</v>
+      </c>
+      <c r="G66" t="s">
+        <v>19</v>
+      </c>
+      <c r="H66" t="s">
+        <v>401</v>
+      </c>
+      <c r="I66" t="s">
+        <v>21</v>
+      </c>
+      <c r="J66" t="s">
+        <v>45</v>
+      </c>
+      <c r="K66" t="s">
+        <v>23</v>
+      </c>
+      <c r="L66" t="s">
+        <v>402</v>
+      </c>
+      <c r="M66" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>404</v>
+      </c>
+      <c r="B67" t="s">
+        <v>405</v>
+      </c>
+      <c r="C67" t="s">
+        <v>15</v>
+      </c>
+      <c r="D67" t="s">
+        <v>406</v>
+      </c>
+      <c r="E67" t="s">
+        <v>363</v>
+      </c>
+      <c r="F67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G67" t="s">
+        <v>19</v>
+      </c>
+      <c r="H67" t="s">
+        <v>407</v>
+      </c>
+      <c r="I67" t="s">
+        <v>21</v>
+      </c>
+      <c r="J67" t="s">
+        <v>22</v>
+      </c>
+      <c r="K67" t="s">
+        <v>23</v>
+      </c>
+      <c r="L67" t="s">
+        <v>408</v>
+      </c>
+      <c r="M67" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>410</v>
+      </c>
+      <c r="B68" t="s">
+        <v>411</v>
+      </c>
+      <c r="C68" t="s">
+        <v>15</v>
+      </c>
+      <c r="D68" t="s">
+        <v>412</v>
+      </c>
+      <c r="E68" t="s">
+        <v>363</v>
+      </c>
+      <c r="F68" t="s">
+        <v>18</v>
+      </c>
+      <c r="G68" t="s">
+        <v>19</v>
+      </c>
+      <c r="H68" t="s">
+        <v>45</v>
+      </c>
+      <c r="I68" t="s">
+        <v>179</v>
+      </c>
+      <c r="J68" t="s">
+        <v>45</v>
+      </c>
+      <c r="K68" t="s">
+        <v>23</v>
+      </c>
+      <c r="L68" t="s">
+        <v>413</v>
+      </c>
+      <c r="M68" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>415</v>
+      </c>
+      <c r="B69" t="s">
+        <v>416</v>
+      </c>
+      <c r="C69" t="s">
+        <v>417</v>
+      </c>
+      <c r="D69" t="s">
+        <v>418</v>
+      </c>
+      <c r="E69" t="s">
+        <v>363</v>
+      </c>
+      <c r="F69" t="s">
+        <v>18</v>
+      </c>
+      <c r="G69" t="s">
+        <v>19</v>
+      </c>
+      <c r="H69" t="s">
+        <v>45</v>
+      </c>
+      <c r="I69" t="s">
+        <v>419</v>
+      </c>
+      <c r="J69" t="s">
+        <v>420</v>
+      </c>
+      <c r="K69" t="s">
+        <v>23</v>
+      </c>
+      <c r="L69" t="s">
+        <v>421</v>
+      </c>
+      <c r="M69" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>423</v>
+      </c>
+      <c r="B70" t="s">
+        <v>424</v>
+      </c>
+      <c r="C70" t="s">
+        <v>15</v>
+      </c>
+      <c r="D70" t="s">
+        <v>425</v>
+      </c>
+      <c r="E70" t="s">
+        <v>363</v>
+      </c>
+      <c r="F70" t="s">
+        <v>18</v>
+      </c>
+      <c r="G70" t="s">
+        <v>19</v>
+      </c>
+      <c r="H70" t="s">
+        <v>20</v>
+      </c>
+      <c r="I70" t="s">
+        <v>21</v>
+      </c>
+      <c r="J70" t="s">
+        <v>45</v>
+      </c>
+      <c r="K70" t="s">
+        <v>23</v>
+      </c>
+      <c r="L70" t="s">
+        <v>426</v>
+      </c>
+      <c r="M70" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>428</v>
+      </c>
+      <c r="B71" t="s">
+        <v>429</v>
+      </c>
+      <c r="C71" t="s">
+        <v>297</v>
+      </c>
+      <c r="D71" t="s">
+        <v>430</v>
+      </c>
+      <c r="E71" t="s">
+        <v>363</v>
+      </c>
+      <c r="F71" t="s">
+        <v>18</v>
+      </c>
+      <c r="G71" t="s">
+        <v>19</v>
+      </c>
+      <c r="H71" t="s">
+        <v>45</v>
+      </c>
+      <c r="I71" t="s">
+        <v>179</v>
+      </c>
+      <c r="J71" t="s">
+        <v>45</v>
+      </c>
+      <c r="K71" t="s">
+        <v>23</v>
+      </c>
+      <c r="L71" t="s">
+        <v>431</v>
+      </c>
+      <c r="M71" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>433</v>
+      </c>
+      <c r="B72" t="s">
+        <v>434</v>
+      </c>
+      <c r="C72" t="s">
+        <v>435</v>
+      </c>
+      <c r="D72" t="s">
+        <v>436</v>
+      </c>
+      <c r="E72" t="s">
+        <v>363</v>
+      </c>
+      <c r="F72" t="s">
+        <v>18</v>
+      </c>
+      <c r="G72" t="s">
+        <v>19</v>
+      </c>
+      <c r="H72" t="s">
+        <v>437</v>
+      </c>
+      <c r="I72" t="s">
+        <v>21</v>
+      </c>
+      <c r="J72" t="s">
+        <v>22</v>
+      </c>
+      <c r="K72" t="s">
+        <v>23</v>
+      </c>
+      <c r="L72" t="s">
+        <v>438</v>
+      </c>
+      <c r="M72" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>440</v>
+      </c>
+      <c r="B73" t="s">
+        <v>441</v>
+      </c>
+      <c r="C73" t="s">
+        <v>15</v>
+      </c>
+      <c r="D73" t="s">
+        <v>442</v>
+      </c>
+      <c r="E73" t="s">
+        <v>363</v>
+      </c>
+      <c r="F73" t="s">
+        <v>18</v>
+      </c>
+      <c r="G73" t="s">
+        <v>19</v>
+      </c>
+      <c r="H73" t="s">
+        <v>20</v>
+      </c>
+      <c r="I73" t="s">
+        <v>21</v>
+      </c>
+      <c r="J73" t="s">
+        <v>443</v>
+      </c>
+      <c r="K73" t="s">
+        <v>23</v>
+      </c>
+      <c r="L73" t="s">
+        <v>444</v>
+      </c>
+      <c r="M73" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>446</v>
+      </c>
+      <c r="B74" t="s">
+        <v>447</v>
+      </c>
+      <c r="C74" t="s">
+        <v>60</v>
+      </c>
+      <c r="D74" t="s">
+        <v>448</v>
+      </c>
+      <c r="E74" t="s">
+        <v>449</v>
+      </c>
+      <c r="F74" t="s">
+        <v>18</v>
+      </c>
+      <c r="G74" t="s">
+        <v>19</v>
+      </c>
+      <c r="H74" t="s">
+        <v>147</v>
+      </c>
+      <c r="I74" t="s">
+        <v>21</v>
+      </c>
+      <c r="J74" t="s">
+        <v>45</v>
+      </c>
+      <c r="K74" t="s">
+        <v>23</v>
+      </c>
+      <c r="L74" t="s">
+        <v>450</v>
+      </c>
+      <c r="M74" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>452</v>
+      </c>
+      <c r="B75" t="s">
+        <v>453</v>
+      </c>
+      <c r="C75" t="s">
+        <v>15</v>
+      </c>
+      <c r="D75" t="s">
+        <v>454</v>
+      </c>
+      <c r="E75" t="s">
+        <v>449</v>
+      </c>
+      <c r="F75" t="s">
+        <v>18</v>
+      </c>
+      <c r="G75" t="s">
+        <v>19</v>
+      </c>
+      <c r="H75" t="s">
+        <v>20</v>
+      </c>
+      <c r="I75" t="s">
+        <v>21</v>
+      </c>
+      <c r="J75" t="s">
+        <v>22</v>
+      </c>
+      <c r="K75" t="s">
+        <v>23</v>
+      </c>
+      <c r="L75" t="s">
+        <v>455</v>
+      </c>
+      <c r="M75" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>457</v>
+      </c>
+      <c r="B76" t="s">
+        <v>458</v>
+      </c>
+      <c r="C76" t="s">
+        <v>159</v>
+      </c>
+      <c r="D76" t="s">
+        <v>459</v>
+      </c>
+      <c r="E76" t="s">
+        <v>245</v>
+      </c>
+      <c r="F76" t="s">
+        <v>18</v>
+      </c>
+      <c r="G76" t="s">
+        <v>19</v>
+      </c>
+      <c r="H76" t="s">
+        <v>215</v>
+      </c>
+      <c r="I76" t="s">
+        <v>21</v>
+      </c>
+      <c r="J76" t="s">
+        <v>45</v>
+      </c>
+      <c r="K76" t="s">
+        <v>23</v>
+      </c>
+      <c r="L76" t="s">
+        <v>460</v>
+      </c>
+      <c r="M76" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>462</v>
+      </c>
+      <c r="B77" t="s">
+        <v>463</v>
+      </c>
+      <c r="C77" t="s">
+        <v>159</v>
+      </c>
+      <c r="D77" t="s">
+        <v>464</v>
+      </c>
+      <c r="E77" t="s">
+        <v>449</v>
+      </c>
+      <c r="F77" t="s">
+        <v>18</v>
+      </c>
+      <c r="G77" t="s">
+        <v>19</v>
+      </c>
+      <c r="H77" t="s">
+        <v>45</v>
+      </c>
+      <c r="I77" t="s">
+        <v>179</v>
+      </c>
+      <c r="J77" t="s">
+        <v>45</v>
+      </c>
+      <c r="K77" t="s">
+        <v>23</v>
+      </c>
+      <c r="L77" t="s">
+        <v>465</v>
+      </c>
+      <c r="M77" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>467</v>
+      </c>
+      <c r="B78" t="s">
+        <v>468</v>
+      </c>
+      <c r="C78" t="s">
+        <v>15</v>
+      </c>
+      <c r="D78" t="s">
+        <v>469</v>
+      </c>
+      <c r="E78" t="s">
+        <v>470</v>
+      </c>
+      <c r="F78" t="s">
+        <v>18</v>
+      </c>
+      <c r="G78" t="s">
+        <v>19</v>
+      </c>
+      <c r="H78" t="s">
+        <v>20</v>
+      </c>
+      <c r="I78" t="s">
+        <v>21</v>
+      </c>
+      <c r="J78" t="s">
+        <v>45</v>
+      </c>
+      <c r="K78" t="s">
+        <v>23</v>
+      </c>
+      <c r="L78" t="s">
+        <v>471</v>
+      </c>
+      <c r="M78" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>473</v>
+      </c>
+      <c r="B79" t="s">
+        <v>474</v>
+      </c>
+      <c r="C79" t="s">
+        <v>43</v>
+      </c>
+      <c r="D79" t="s">
+        <v>475</v>
+      </c>
+      <c r="E79" t="s">
+        <v>470</v>
+      </c>
+      <c r="F79" t="s">
+        <v>18</v>
+      </c>
+      <c r="G79" t="s">
+        <v>19</v>
+      </c>
+      <c r="H79" t="s">
+        <v>45</v>
+      </c>
+      <c r="I79" t="s">
+        <v>179</v>
+      </c>
+      <c r="J79" t="s">
+        <v>45</v>
+      </c>
+      <c r="K79" t="s">
+        <v>23</v>
+      </c>
+      <c r="L79" t="s">
+        <v>476</v>
+      </c>
+      <c r="M79" t="s">
+        <v>477</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>478</v>
+      </c>
+      <c r="B80" t="s">
+        <v>479</v>
+      </c>
+      <c r="C80" t="s">
+        <v>15</v>
+      </c>
+      <c r="D80" t="s">
+        <v>480</v>
+      </c>
+      <c r="E80" t="s">
+        <v>470</v>
+      </c>
+      <c r="F80" t="s">
+        <v>18</v>
+      </c>
+      <c r="G80" t="s">
+        <v>19</v>
+      </c>
+      <c r="H80" t="s">
+        <v>401</v>
+      </c>
+      <c r="I80" t="s">
+        <v>21</v>
+      </c>
+      <c r="J80" t="s">
+        <v>45</v>
+      </c>
+      <c r="K80" t="s">
+        <v>23</v>
+      </c>
+      <c r="L80" t="s">
+        <v>481</v>
+      </c>
+      <c r="M80" t="s">
+        <v>482</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>483</v>
+      </c>
+      <c r="B81" t="s">
+        <v>484</v>
+      </c>
+      <c r="C81" t="s">
+        <v>297</v>
+      </c>
+      <c r="D81" t="s">
+        <v>485</v>
+      </c>
+      <c r="E81" t="s">
+        <v>470</v>
+      </c>
+      <c r="F81" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" t="s">
+        <v>19</v>
+      </c>
+      <c r="H81" t="s">
+        <v>45</v>
+      </c>
+      <c r="I81" t="s">
+        <v>179</v>
+      </c>
+      <c r="J81" t="s">
+        <v>45</v>
+      </c>
+      <c r="K81" t="s">
+        <v>23</v>
+      </c>
+      <c r="L81" t="s">
+        <v>486</v>
+      </c>
+      <c r="M81" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>488</v>
+      </c>
+      <c r="B82" t="s">
+        <v>489</v>
+      </c>
+      <c r="C82" t="s">
+        <v>43</v>
+      </c>
+      <c r="D82" t="s">
+        <v>490</v>
+      </c>
+      <c r="E82" t="s">
+        <v>470</v>
+      </c>
+      <c r="F82" t="s">
+        <v>18</v>
+      </c>
+      <c r="G82" t="s">
+        <v>19</v>
+      </c>
+      <c r="H82" t="s">
+        <v>45</v>
+      </c>
+      <c r="I82" t="s">
+        <v>179</v>
+      </c>
+      <c r="J82" t="s">
+        <v>45</v>
+      </c>
+      <c r="K82" t="s">
+        <v>23</v>
+      </c>
+      <c r="L82" t="s">
+        <v>491</v>
+      </c>
+      <c r="M82" t="s">
+        <v>492</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
